--- a/research/traditional_assets/database/data/egypt/egypt_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_auto_truck.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1914522199477373</v>
+        <v>0.1910563274528549</v>
       </c>
       <c r="C2">
-        <v>908.6366966330779</v>
+        <v>902.2509832316108</v>
       </c>
       <c r="D2">
-        <v>755.9366966330779</v>
+        <v>757.9969832316108</v>
       </c>
       <c r="E2">
-        <v>-478.8</v>
+        <v>-470.354</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.446</v>
       </c>
       <c r="G2">
         <v>152.7</v>
@@ -1457,28 +1457,28 @@
         <v>144.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4248338</v>
       </c>
       <c r="N2">
-        <v>144.775</v>
+        <v>144.3501662</v>
       </c>
       <c r="O2">
-        <v>32.574375</v>
+        <v>32.478787395</v>
       </c>
       <c r="P2">
-        <v>112.200625</v>
+        <v>111.871378805</v>
       </c>
       <c r="Q2">
-        <v>129.800625</v>
+        <v>129.471378805</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1914522199477373</v>
+        <v>0.1925924267200555</v>
       </c>
       <c r="T2">
-        <v>1.015551736571413</v>
+        <v>1.023501762792048</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>340.7803239761055</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1910563274528549</v>
+        <v>0.1906604349579725</v>
       </c>
       <c r="C3">
-        <v>902.2509832316108</v>
+        <v>895.8765310416939</v>
       </c>
       <c r="D3">
-        <v>757.9969832316108</v>
+        <v>760.068531041694</v>
       </c>
       <c r="E3">
-        <v>-470.354</v>
+        <v>-461.908</v>
       </c>
       <c r="F3">
-        <v>8.446</v>
+        <v>16.892</v>
       </c>
       <c r="G3">
         <v>152.7</v>
@@ -1539,28 +1539,28 @@
         <v>144.775</v>
       </c>
       <c r="M3">
-        <v>0.4248338</v>
+        <v>0.8496676</v>
       </c>
       <c r="N3">
-        <v>144.3501662</v>
+        <v>143.9253324</v>
       </c>
       <c r="O3">
-        <v>32.478787395</v>
+        <v>32.38319978999999</v>
       </c>
       <c r="P3">
-        <v>111.871378805</v>
+        <v>111.54213261</v>
       </c>
       <c r="Q3">
-        <v>129.471378805</v>
+        <v>129.14213261</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1925924267200555</v>
+        <v>0.1937559030183393</v>
       </c>
       <c r="T3">
-        <v>1.023501762792048</v>
+        <v>1.031614034445757</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>340.7803239761055</v>
+        <v>170.3901619880527</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1906604349579725</v>
+        <v>0.1902645424630901</v>
       </c>
       <c r="C4">
-        <v>895.8765310416939</v>
+        <v>889.5134326444356</v>
       </c>
       <c r="D4">
-        <v>760.068531041694</v>
+        <v>762.1514326444357</v>
       </c>
       <c r="E4">
-        <v>-461.908</v>
+        <v>-453.462</v>
       </c>
       <c r="F4">
-        <v>16.892</v>
+        <v>25.338</v>
       </c>
       <c r="G4">
         <v>152.7</v>
@@ -1621,28 +1621,28 @@
         <v>144.775</v>
       </c>
       <c r="M4">
-        <v>0.8496676</v>
+        <v>1.2745014</v>
       </c>
       <c r="N4">
-        <v>143.9253324</v>
+        <v>143.5004986</v>
       </c>
       <c r="O4">
-        <v>32.38319978999999</v>
+        <v>32.287612185</v>
       </c>
       <c r="P4">
-        <v>111.54213261</v>
+        <v>111.212886415</v>
       </c>
       <c r="Q4">
-        <v>129.14213261</v>
+        <v>128.812886415</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1937559030183393</v>
+        <v>0.1949433685186496</v>
       </c>
       <c r="T4">
-        <v>1.031614034445757</v>
+        <v>1.039893569432532</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>170.3901619880527</v>
+        <v>113.5934413253685</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1902645424630901</v>
+        <v>0.1898686499682077</v>
       </c>
       <c r="C5">
-        <v>889.5134326444356</v>
+        <v>883.1617816385741</v>
       </c>
       <c r="D5">
-        <v>762.1514326444357</v>
+        <v>764.245781638574</v>
       </c>
       <c r="E5">
-        <v>-453.462</v>
+        <v>-445.016</v>
       </c>
       <c r="F5">
-        <v>25.338</v>
+        <v>33.784</v>
       </c>
       <c r="G5">
         <v>152.7</v>
@@ -1703,28 +1703,28 @@
         <v>144.775</v>
       </c>
       <c r="M5">
-        <v>1.2745014</v>
+        <v>1.6993352</v>
       </c>
       <c r="N5">
-        <v>143.5004986</v>
+        <v>143.0756648</v>
       </c>
       <c r="O5">
-        <v>32.287612185</v>
+        <v>32.19202457999999</v>
       </c>
       <c r="P5">
-        <v>111.212886415</v>
+        <v>110.88364022</v>
       </c>
       <c r="Q5">
-        <v>128.812886415</v>
+        <v>128.48364022</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1949433685186496</v>
+        <v>0.1961555728835497</v>
       </c>
       <c r="T5">
-        <v>1.039893569432532</v>
+        <v>1.048345594731532</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>113.5934413253685</v>
+        <v>85.19508099402636</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1898686499682077</v>
+        <v>0.1894727574733253</v>
       </c>
       <c r="C6">
-        <v>883.1617816385741</v>
+        <v>876.821672654499</v>
       </c>
       <c r="D6">
-        <v>764.245781638574</v>
+        <v>766.351672654499</v>
       </c>
       <c r="E6">
-        <v>-445.016</v>
+        <v>-436.57</v>
       </c>
       <c r="F6">
-        <v>33.784</v>
+        <v>42.23</v>
       </c>
       <c r="G6">
         <v>152.7</v>
@@ -1785,28 +1785,28 @@
         <v>144.775</v>
       </c>
       <c r="M6">
-        <v>1.6993352</v>
+        <v>2.124169</v>
       </c>
       <c r="N6">
-        <v>143.0756648</v>
+        <v>142.650831</v>
       </c>
       <c r="O6">
-        <v>32.19202457999999</v>
+        <v>32.096436975</v>
       </c>
       <c r="P6">
-        <v>110.88364022</v>
+        <v>110.554394025</v>
       </c>
       <c r="Q6">
-        <v>128.48364022</v>
+        <v>128.154394025</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1961555728835497</v>
+        <v>0.1973932973403424</v>
       </c>
       <c r="T6">
-        <v>1.048345594731532</v>
+        <v>1.056975557405247</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.19508099402636</v>
+        <v>68.15606479522108</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1894727574733253</v>
+        <v>0.1890768649784429</v>
       </c>
       <c r="C7">
-        <v>876.821672654499</v>
+        <v>870.4932013685044</v>
       </c>
       <c r="D7">
-        <v>766.351672654499</v>
+        <v>768.4692013685044</v>
       </c>
       <c r="E7">
-        <v>-436.57</v>
+        <v>-428.124</v>
       </c>
       <c r="F7">
-        <v>42.23</v>
+        <v>50.676</v>
       </c>
       <c r="G7">
         <v>152.7</v>
@@ -1867,28 +1867,28 @@
         <v>144.775</v>
       </c>
       <c r="M7">
-        <v>2.124169</v>
+        <v>2.5490028</v>
       </c>
       <c r="N7">
-        <v>142.650831</v>
+        <v>142.2259972</v>
       </c>
       <c r="O7">
-        <v>32.096436975</v>
+        <v>32.00084936999999</v>
       </c>
       <c r="P7">
-        <v>110.554394025</v>
+        <v>110.22514783</v>
       </c>
       <c r="Q7">
-        <v>128.154394025</v>
+        <v>127.82514783</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1973932973403424</v>
+        <v>0.1986573563600456</v>
       </c>
       <c r="T7">
-        <v>1.056975557405247</v>
+        <v>1.065789136306063</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.15606479522108</v>
+        <v>56.79672066268424</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1890768649784429</v>
+        <v>0.1886809724835605</v>
       </c>
       <c r="C8">
-        <v>870.4932013685044</v>
+        <v>864.1764645172772</v>
       </c>
       <c r="D8">
-        <v>768.4692013685044</v>
+        <v>770.5984645172771</v>
       </c>
       <c r="E8">
-        <v>-428.124</v>
+        <v>-419.678</v>
       </c>
       <c r="F8">
-        <v>50.676</v>
+        <v>59.12199999999999</v>
       </c>
       <c r="G8">
         <v>152.7</v>
@@ -1949,28 +1949,28 @@
         <v>144.775</v>
       </c>
       <c r="M8">
-        <v>2.5490028</v>
+        <v>2.973836599999999</v>
       </c>
       <c r="N8">
-        <v>142.2259972</v>
+        <v>141.8011634</v>
       </c>
       <c r="O8">
-        <v>32.00084936999999</v>
+        <v>31.905261765</v>
       </c>
       <c r="P8">
-        <v>110.22514783</v>
+        <v>109.895901635</v>
       </c>
       <c r="Q8">
-        <v>127.82514783</v>
+        <v>127.495901635</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1986573563600456</v>
+        <v>0.1999485994446887</v>
       </c>
       <c r="T8">
-        <v>1.065789136306063</v>
+        <v>1.074792254538079</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.79672066268424</v>
+        <v>48.68290342515793</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1886809724835605</v>
+        <v>0.1882850799886781</v>
       </c>
       <c r="C9">
-        <v>864.1764645172772</v>
+        <v>857.8715599126303</v>
       </c>
       <c r="D9">
-        <v>770.5984645172772</v>
+        <v>772.7395599126303</v>
       </c>
       <c r="E9">
-        <v>-419.678</v>
+        <v>-411.232</v>
       </c>
       <c r="F9">
-        <v>59.12200000000001</v>
+        <v>67.568</v>
       </c>
       <c r="G9">
         <v>152.7</v>
@@ -2031,28 +2031,28 @@
         <v>144.775</v>
       </c>
       <c r="M9">
-        <v>2.9738366</v>
+        <v>3.3986704</v>
       </c>
       <c r="N9">
-        <v>141.8011634</v>
+        <v>141.3763296</v>
       </c>
       <c r="O9">
-        <v>31.905261765</v>
+        <v>31.80967416</v>
       </c>
       <c r="P9">
-        <v>109.895901635</v>
+        <v>109.56665544</v>
       </c>
       <c r="Q9">
-        <v>127.495901635</v>
+        <v>127.16665544</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1999485994446887</v>
+        <v>0.2012679130311718</v>
       </c>
       <c r="T9">
-        <v>1.074792254538079</v>
+        <v>1.08399109273166</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.68290342515792</v>
+        <v>42.59754049701318</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1882850799886781</v>
+        <v>0.1878891874937957</v>
       </c>
       <c r="C10">
-        <v>857.8715599126303</v>
+        <v>851.5785864564799</v>
       </c>
       <c r="D10">
-        <v>772.7395599126303</v>
+        <v>774.89258645648</v>
       </c>
       <c r="E10">
-        <v>-411.232</v>
+        <v>-402.786</v>
       </c>
       <c r="F10">
-        <v>67.568</v>
+        <v>76.014</v>
       </c>
       <c r="G10">
         <v>152.7</v>
@@ -2113,28 +2113,28 @@
         <v>144.775</v>
       </c>
       <c r="M10">
-        <v>3.3986704</v>
+        <v>3.823504199999999</v>
       </c>
       <c r="N10">
-        <v>141.3763296</v>
+        <v>140.9514958</v>
       </c>
       <c r="O10">
-        <v>31.80967416</v>
+        <v>31.71408655499999</v>
       </c>
       <c r="P10">
-        <v>109.56665544</v>
+        <v>109.237409245</v>
       </c>
       <c r="Q10">
-        <v>127.16665544</v>
+        <v>126.837409245</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2012679130311718</v>
+        <v>0.2026162225206546</v>
       </c>
       <c r="T10">
-        <v>1.08399109273166</v>
+        <v>1.093392103193233</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.59754049701318</v>
+        <v>37.8644804417895</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1878891874937957</v>
+        <v>0.1874932949989132</v>
       </c>
       <c r="C11">
-        <v>851.5785864564799</v>
+        <v>845.2976441560734</v>
       </c>
       <c r="D11">
-        <v>774.89258645648</v>
+        <v>777.0576441560734</v>
       </c>
       <c r="E11">
-        <v>-402.786</v>
+        <v>-394.34</v>
       </c>
       <c r="F11">
-        <v>76.014</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="G11">
         <v>152.7</v>
@@ -2195,28 +2195,28 @@
         <v>144.775</v>
       </c>
       <c r="M11">
-        <v>3.823504199999999</v>
+        <v>4.248338</v>
       </c>
       <c r="N11">
-        <v>140.9514958</v>
+        <v>140.526662</v>
       </c>
       <c r="O11">
-        <v>31.71408655499999</v>
+        <v>31.61849895</v>
       </c>
       <c r="P11">
-        <v>109.237409245</v>
+        <v>108.90816305</v>
       </c>
       <c r="Q11">
-        <v>126.837409245</v>
+        <v>126.50816305</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2026162225206546</v>
+        <v>0.2039944944432369</v>
       </c>
       <c r="T11">
-        <v>1.093392103193233</v>
+        <v>1.103002024998396</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.8644804417895</v>
+        <v>34.07803239761055</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1874932949989132</v>
+        <v>0.1870974025040308</v>
       </c>
       <c r="C12">
-        <v>845.2976441560734</v>
+        <v>839.0288341394746</v>
       </c>
       <c r="D12">
-        <v>777.0576441560734</v>
+        <v>779.2348341394745</v>
       </c>
       <c r="E12">
-        <v>-394.34</v>
+        <v>-385.894</v>
       </c>
       <c r="F12">
-        <v>84.46000000000001</v>
+        <v>92.90600000000001</v>
       </c>
       <c r="G12">
         <v>152.7</v>
@@ -2277,28 +2277,28 @@
         <v>144.775</v>
       </c>
       <c r="M12">
-        <v>4.248338</v>
+        <v>4.6731718</v>
       </c>
       <c r="N12">
-        <v>140.526662</v>
+        <v>140.1018282</v>
       </c>
       <c r="O12">
-        <v>31.61849895</v>
+        <v>31.52291134499999</v>
       </c>
       <c r="P12">
-        <v>108.90816305</v>
+        <v>108.578916855</v>
       </c>
       <c r="Q12">
-        <v>126.50816305</v>
+        <v>126.178916855</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2039944944432369</v>
+        <v>0.205403738768574</v>
       </c>
       <c r="T12">
-        <v>1.103002024998396</v>
+        <v>1.112827900102551</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.07803239761054</v>
+        <v>30.98002945237322</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1870974025040308</v>
+        <v>0.1867015100091485</v>
       </c>
       <c r="C13">
-        <v>839.0288341394746</v>
+        <v>832.7722586713102</v>
       </c>
       <c r="D13">
-        <v>779.2348341394745</v>
+        <v>781.4242586713102</v>
       </c>
       <c r="E13">
-        <v>-385.894</v>
+        <v>-377.448</v>
       </c>
       <c r="F13">
-        <v>92.90600000000001</v>
+        <v>101.352</v>
       </c>
       <c r="G13">
         <v>152.7</v>
@@ -2359,28 +2359,28 @@
         <v>144.775</v>
       </c>
       <c r="M13">
-        <v>4.6731718</v>
+        <v>5.0980056</v>
       </c>
       <c r="N13">
-        <v>140.1018282</v>
+        <v>139.6769944</v>
       </c>
       <c r="O13">
-        <v>31.52291134499999</v>
+        <v>31.42732374</v>
       </c>
       <c r="P13">
-        <v>108.578916855</v>
+        <v>108.24967066</v>
       </c>
       <c r="Q13">
-        <v>126.178916855</v>
+        <v>125.84967066</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.205403738768574</v>
+        <v>0.2068450113740323</v>
       </c>
       <c r="T13">
-        <v>1.112827900102551</v>
+        <v>1.122877090549983</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.98002945237322</v>
+        <v>28.39836033134212</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1867015100091485</v>
+        <v>0.186305617514266</v>
       </c>
       <c r="C14">
-        <v>832.7722586713102</v>
+        <v>826.5280211687823</v>
       </c>
       <c r="D14">
-        <v>781.4242586713102</v>
+        <v>783.6260211687822</v>
       </c>
       <c r="E14">
-        <v>-377.448</v>
+        <v>-369.002</v>
       </c>
       <c r="F14">
-        <v>101.352</v>
+        <v>109.798</v>
       </c>
       <c r="G14">
         <v>152.7</v>
@@ -2441,28 +2441,28 @@
         <v>144.775</v>
       </c>
       <c r="M14">
-        <v>5.0980056</v>
+        <v>5.5228394</v>
       </c>
       <c r="N14">
-        <v>139.6769944</v>
+        <v>139.2521606</v>
       </c>
       <c r="O14">
-        <v>31.42732374</v>
+        <v>31.33173613499999</v>
       </c>
       <c r="P14">
-        <v>108.24967066</v>
+        <v>107.920424465</v>
       </c>
       <c r="Q14">
-        <v>125.84967066</v>
+        <v>125.520424465</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2068450113740323</v>
+        <v>0.2083194166830644</v>
       </c>
       <c r="T14">
-        <v>1.122877090549983</v>
+        <v>1.133157296869769</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.39836033134212</v>
+        <v>26.21387107508503</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.186305617514266</v>
+        <v>0.1859097250193836</v>
       </c>
       <c r="C15">
-        <v>826.5280211687823</v>
+        <v>820.2962262179491</v>
       </c>
       <c r="D15">
-        <v>783.6260211687822</v>
+        <v>785.8402262179491</v>
       </c>
       <c r="E15">
-        <v>-369.002</v>
+        <v>-360.556</v>
       </c>
       <c r="F15">
-        <v>109.798</v>
+        <v>118.244</v>
       </c>
       <c r="G15">
         <v>152.7</v>
@@ -2523,28 +2523,28 @@
         <v>144.775</v>
       </c>
       <c r="M15">
-        <v>5.5228394</v>
+        <v>5.947673200000001</v>
       </c>
       <c r="N15">
-        <v>139.2521606</v>
+        <v>138.8273268</v>
       </c>
       <c r="O15">
-        <v>31.33173613499999</v>
+        <v>31.23614853</v>
       </c>
       <c r="P15">
-        <v>107.920424465</v>
+        <v>107.59117827</v>
       </c>
       <c r="Q15">
-        <v>125.520424465</v>
+        <v>125.19117827</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2083194166830644</v>
+        <v>0.2098281104876553</v>
       </c>
       <c r="T15">
-        <v>1.133157296869769</v>
+        <v>1.143676577755132</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.21387107508503</v>
+        <v>24.34145171257896</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1859097250193836</v>
+        <v>0.1855138325245012</v>
       </c>
       <c r="C16">
-        <v>820.2962262179491</v>
+        <v>814.0769795902884</v>
       </c>
       <c r="D16">
-        <v>785.8402262179491</v>
+        <v>788.0669795902884</v>
       </c>
       <c r="E16">
-        <v>-360.556</v>
+        <v>-352.11</v>
       </c>
       <c r="F16">
-        <v>118.244</v>
+        <v>126.69</v>
       </c>
       <c r="G16">
         <v>152.7</v>
@@ -2605,28 +2605,28 @@
         <v>144.775</v>
       </c>
       <c r="M16">
-        <v>5.947673200000001</v>
+        <v>6.372507000000001</v>
       </c>
       <c r="N16">
-        <v>138.8273268</v>
+        <v>138.402493</v>
       </c>
       <c r="O16">
-        <v>31.23614853</v>
+        <v>31.14056092499999</v>
       </c>
       <c r="P16">
-        <v>107.59117827</v>
+        <v>107.261932075</v>
       </c>
       <c r="Q16">
-        <v>125.19117827</v>
+        <v>124.861932075</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2098281104876553</v>
+        <v>0.2113723029700014</v>
       </c>
       <c r="T16">
-        <v>1.143676577755132</v>
+        <v>1.154443371131915</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.34145171257896</v>
+        <v>22.71868826507369</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1855138325245012</v>
+        <v>0.1851179400296188</v>
       </c>
       <c r="C17">
-        <v>814.0769795902884</v>
+        <v>807.8703882595387</v>
       </c>
       <c r="D17">
-        <v>788.0669795902884</v>
+        <v>790.3063882595387</v>
       </c>
       <c r="E17">
-        <v>-352.11</v>
+        <v>-343.664</v>
       </c>
       <c r="F17">
-        <v>126.69</v>
+        <v>135.136</v>
       </c>
       <c r="G17">
         <v>152.7</v>
@@ -2687,28 +2687,28 @@
         <v>144.775</v>
       </c>
       <c r="M17">
-        <v>6.372507</v>
+        <v>6.7973408</v>
       </c>
       <c r="N17">
-        <v>138.402493</v>
+        <v>137.9776592</v>
       </c>
       <c r="O17">
-        <v>31.14056092499999</v>
+        <v>31.04497332</v>
       </c>
       <c r="P17">
-        <v>107.261932075</v>
+        <v>106.93268588</v>
       </c>
       <c r="Q17">
-        <v>124.861932075</v>
+        <v>124.53268588</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2113723029700014</v>
+        <v>0.2129532619400224</v>
       </c>
       <c r="T17">
-        <v>1.154443371131915</v>
+        <v>1.165466516731955</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.71868826507369</v>
+        <v>21.29877024850659</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1851179400296188</v>
+        <v>0.1847220475347364</v>
       </c>
       <c r="C18">
-        <v>807.8703882595387</v>
+        <v>801.6765604188307</v>
       </c>
       <c r="D18">
-        <v>790.3063882595387</v>
+        <v>792.5585604188307</v>
       </c>
       <c r="E18">
-        <v>-343.664</v>
+        <v>-335.218</v>
       </c>
       <c r="F18">
-        <v>135.136</v>
+        <v>143.582</v>
       </c>
       <c r="G18">
         <v>152.7</v>
@@ -2769,28 +2769,28 @@
         <v>144.775</v>
       </c>
       <c r="M18">
-        <v>6.7973408</v>
+        <v>7.222174600000001</v>
       </c>
       <c r="N18">
-        <v>137.9776592</v>
+        <v>137.5528254</v>
       </c>
       <c r="O18">
-        <v>31.04497332</v>
+        <v>30.949385715</v>
       </c>
       <c r="P18">
-        <v>106.93268588</v>
+        <v>106.603439685</v>
       </c>
       <c r="Q18">
-        <v>124.53268588</v>
+        <v>124.203439685</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2129532619400224</v>
+        <v>0.2145723163069113</v>
       </c>
       <c r="T18">
-        <v>1.165466516731955</v>
+        <v>1.176755280298261</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.29877024850659</v>
+        <v>20.04590141035914</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1847220475347364</v>
+        <v>0.1843261550398539</v>
       </c>
       <c r="C19">
-        <v>801.6765604188307</v>
+        <v>795.495605498111</v>
       </c>
       <c r="D19">
-        <v>792.5585604188307</v>
+        <v>794.8236054981111</v>
       </c>
       <c r="E19">
-        <v>-335.218</v>
+        <v>-326.772</v>
       </c>
       <c r="F19">
-        <v>143.582</v>
+        <v>152.028</v>
       </c>
       <c r="G19">
         <v>152.7</v>
@@ -2851,28 +2851,28 @@
         <v>144.775</v>
       </c>
       <c r="M19">
-        <v>7.222174600000001</v>
+        <v>7.647008400000001</v>
       </c>
       <c r="N19">
-        <v>137.5528254</v>
+        <v>137.1279916</v>
       </c>
       <c r="O19">
-        <v>30.949385715</v>
+        <v>30.85379811</v>
       </c>
       <c r="P19">
-        <v>106.603439685</v>
+        <v>106.27419349</v>
       </c>
       <c r="Q19">
-        <v>124.203439685</v>
+        <v>123.87419349</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2145723163069113</v>
+        <v>0.2162308598047</v>
       </c>
       <c r="T19">
-        <v>1.176755280298261</v>
+        <v>1.188319379561306</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.04590141035914</v>
+        <v>18.93224022089474</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.184326155039854</v>
+        <v>0.1839302625449716</v>
       </c>
       <c r="C20">
-        <v>795.4956054981108</v>
+        <v>789.3276341818658</v>
       </c>
       <c r="D20">
-        <v>794.8236054981109</v>
+        <v>797.101634181866</v>
       </c>
       <c r="E20">
-        <v>-326.772</v>
+        <v>-318.326</v>
       </c>
       <c r="F20">
-        <v>152.028</v>
+        <v>160.474</v>
       </c>
       <c r="G20">
         <v>152.7</v>
@@ -2933,28 +2933,28 @@
         <v>144.775</v>
       </c>
       <c r="M20">
-        <v>7.647008399999999</v>
+        <v>8.071842200000001</v>
       </c>
       <c r="N20">
-        <v>137.1279916</v>
+        <v>136.7031578</v>
       </c>
       <c r="O20">
-        <v>30.85379811</v>
+        <v>30.758210505</v>
       </c>
       <c r="P20">
-        <v>106.27419349</v>
+        <v>105.944947295</v>
       </c>
       <c r="Q20">
-        <v>123.87419349</v>
+        <v>123.544947295</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2162308598047</v>
+        <v>0.217930354993792</v>
       </c>
       <c r="T20">
-        <v>1.188319379561306</v>
+        <v>1.200169012139488</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.93224022089475</v>
+        <v>17.93580652505818</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1839302625449716</v>
+        <v>0.1835343700500892</v>
       </c>
       <c r="C21">
-        <v>789.3276341818658</v>
+        <v>783.1727584271528</v>
       </c>
       <c r="D21">
-        <v>797.101634181866</v>
+        <v>799.3927584271529</v>
       </c>
       <c r="E21">
-        <v>-318.326</v>
+        <v>-309.88</v>
       </c>
       <c r="F21">
-        <v>160.474</v>
+        <v>168.92</v>
       </c>
       <c r="G21">
         <v>152.7</v>
@@ -3015,28 +3015,28 @@
         <v>144.775</v>
       </c>
       <c r="M21">
-        <v>8.071842200000001</v>
+        <v>8.496676000000001</v>
       </c>
       <c r="N21">
-        <v>136.7031578</v>
+        <v>136.278324</v>
       </c>
       <c r="O21">
-        <v>30.758210505</v>
+        <v>30.6626229</v>
       </c>
       <c r="P21">
-        <v>105.944947295</v>
+        <v>105.6157011</v>
       </c>
       <c r="Q21">
-        <v>123.544947295</v>
+        <v>123.2157011</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.217930354993792</v>
+        <v>0.2196723375626115</v>
       </c>
       <c r="T21">
-        <v>1.200169012139488</v>
+        <v>1.212314885532124</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.93580652505818</v>
+        <v>17.03901619880527</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1835343700500892</v>
+        <v>0.1831384775552068</v>
       </c>
       <c r="C22">
-        <v>783.1727584271528</v>
+        <v>777.0310914819406</v>
       </c>
       <c r="D22">
-        <v>799.3927584271529</v>
+        <v>801.6970914819407</v>
       </c>
       <c r="E22">
-        <v>-309.88</v>
+        <v>-301.434</v>
       </c>
       <c r="F22">
-        <v>168.92</v>
+        <v>177.366</v>
       </c>
       <c r="G22">
         <v>152.7</v>
@@ -3097,28 +3097,28 @@
         <v>144.775</v>
       </c>
       <c r="M22">
-        <v>8.496676000000001</v>
+        <v>8.921509800000001</v>
       </c>
       <c r="N22">
-        <v>136.278324</v>
+        <v>135.8534902</v>
       </c>
       <c r="O22">
-        <v>30.6626229</v>
+        <v>30.567035295</v>
       </c>
       <c r="P22">
-        <v>105.6157011</v>
+        <v>105.286454905</v>
       </c>
       <c r="Q22">
-        <v>123.2157011</v>
+        <v>122.886454905</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2196723375626115</v>
+        <v>0.2214584209559579</v>
       </c>
       <c r="T22">
-        <v>1.212314885532124</v>
+        <v>1.224768249390397</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.03901619880527</v>
+        <v>16.22763447505264</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1831384775552068</v>
+        <v>0.1827425850603244</v>
       </c>
       <c r="C23">
-        <v>777.0310914819406</v>
+        <v>770.9027479037683</v>
       </c>
       <c r="D23">
-        <v>801.6970914819407</v>
+        <v>804.0147479037682</v>
       </c>
       <c r="E23">
-        <v>-301.434</v>
+        <v>-292.988</v>
       </c>
       <c r="F23">
-        <v>177.366</v>
+        <v>185.812</v>
       </c>
       <c r="G23">
         <v>152.7</v>
@@ -3179,28 +3179,28 @@
         <v>144.775</v>
       </c>
       <c r="M23">
-        <v>8.921509799999999</v>
+        <v>9.346343600000001</v>
       </c>
       <c r="N23">
-        <v>135.8534902</v>
+        <v>135.4286564</v>
       </c>
       <c r="O23">
-        <v>30.567035295</v>
+        <v>30.47144768999999</v>
       </c>
       <c r="P23">
-        <v>105.286454905</v>
+        <v>104.95720871</v>
       </c>
       <c r="Q23">
-        <v>122.886454905</v>
+        <v>122.55720871</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2214584209559579</v>
+        <v>0.2232903013593902</v>
       </c>
       <c r="T23">
-        <v>1.224768249390397</v>
+        <v>1.237540930270677</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.22763447505264</v>
+        <v>15.49001472618661</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1827425850603244</v>
+        <v>0.1823466925654419</v>
       </c>
       <c r="C24">
-        <v>770.9027479037683</v>
+        <v>764.787843578732</v>
       </c>
       <c r="D24">
-        <v>804.0147479037682</v>
+        <v>806.345843578732</v>
       </c>
       <c r="E24">
-        <v>-292.988</v>
+        <v>-284.542</v>
       </c>
       <c r="F24">
-        <v>185.812</v>
+        <v>194.258</v>
       </c>
       <c r="G24">
         <v>152.7</v>
@@ -3261,28 +3261,28 @@
         <v>144.775</v>
       </c>
       <c r="M24">
-        <v>9.346343600000001</v>
+        <v>9.771177399999999</v>
       </c>
       <c r="N24">
-        <v>135.4286564</v>
+        <v>135.0038226</v>
       </c>
       <c r="O24">
-        <v>30.47144768999999</v>
+        <v>30.375860085</v>
       </c>
       <c r="P24">
-        <v>104.95720871</v>
+        <v>104.627962515</v>
       </c>
       <c r="Q24">
-        <v>122.55720871</v>
+        <v>122.227962515</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2232903013593902</v>
+        <v>0.2251697630720025</v>
       </c>
       <c r="T24">
-        <v>1.237540930270677</v>
+        <v>1.250645369095899</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.49001472618661</v>
+        <v>14.81653582504806</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1823466925654419</v>
+        <v>0.1819508000705596</v>
       </c>
       <c r="C25">
-        <v>764.787843578732</v>
+        <v>758.6864957407977</v>
       </c>
       <c r="D25">
-        <v>806.345843578732</v>
+        <v>808.6904957407977</v>
       </c>
       <c r="E25">
-        <v>-284.542</v>
+        <v>-276.096</v>
       </c>
       <c r="F25">
-        <v>194.258</v>
+        <v>202.704</v>
       </c>
       <c r="G25">
         <v>152.7</v>
@@ -3343,28 +3343,28 @@
         <v>144.775</v>
       </c>
       <c r="M25">
-        <v>9.771177399999999</v>
+        <v>10.1960112</v>
       </c>
       <c r="N25">
-        <v>135.0038226</v>
+        <v>134.5789888</v>
       </c>
       <c r="O25">
-        <v>30.375860085</v>
+        <v>30.28027248</v>
       </c>
       <c r="P25">
-        <v>104.627962515</v>
+        <v>104.29871632</v>
       </c>
       <c r="Q25">
-        <v>122.227962515</v>
+        <v>121.89871632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2251697630720025</v>
+        <v>0.2270986843033678</v>
       </c>
       <c r="T25">
-        <v>1.250645369095899</v>
+        <v>1.264094661574417</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.81653582504806</v>
+        <v>14.19918016567106</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1819508000705596</v>
+        <v>0.1815549075756771</v>
       </c>
       <c r="C26">
-        <v>758.6864957407977</v>
+        <v>752.5988229914575</v>
       </c>
       <c r="D26">
-        <v>808.6904957407977</v>
+        <v>811.0488229914575</v>
       </c>
       <c r="E26">
-        <v>-276.096</v>
+        <v>-267.65</v>
       </c>
       <c r="F26">
-        <v>202.704</v>
+        <v>211.15</v>
       </c>
       <c r="G26">
         <v>152.7</v>
@@ -3425,28 +3425,28 @@
         <v>144.775</v>
       </c>
       <c r="M26">
-        <v>10.1960112</v>
+        <v>10.620845</v>
       </c>
       <c r="N26">
-        <v>134.5789888</v>
+        <v>134.154155</v>
       </c>
       <c r="O26">
-        <v>30.28027248</v>
+        <v>30.18468487499999</v>
       </c>
       <c r="P26">
-        <v>104.29871632</v>
+        <v>103.969470125</v>
       </c>
       <c r="Q26">
-        <v>121.89871632</v>
+        <v>121.569470125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2270986843033678</v>
+        <v>0.2290790434342362</v>
       </c>
       <c r="T26">
-        <v>1.264094661574417</v>
+        <v>1.277902601852361</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.19918016567106</v>
+        <v>13.63121295904422</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1815549075756771</v>
+        <v>0.1811590150807947</v>
       </c>
       <c r="C27">
-        <v>752.5988229914575</v>
+        <v>746.5249453197257</v>
       </c>
       <c r="D27">
-        <v>811.0488229914575</v>
+        <v>813.4209453197257</v>
       </c>
       <c r="E27">
-        <v>-267.65</v>
+        <v>-259.204</v>
       </c>
       <c r="F27">
-        <v>211.15</v>
+        <v>219.596</v>
       </c>
       <c r="G27">
         <v>152.7</v>
@@ -3507,28 +3507,28 @@
         <v>144.775</v>
       </c>
       <c r="M27">
-        <v>10.620845</v>
+        <v>11.0456788</v>
       </c>
       <c r="N27">
-        <v>134.154155</v>
+        <v>133.7293212</v>
       </c>
       <c r="O27">
-        <v>30.18468487499999</v>
+        <v>30.08909727</v>
       </c>
       <c r="P27">
-        <v>103.969470125</v>
+        <v>103.64022393</v>
       </c>
       <c r="Q27">
-        <v>121.569470125</v>
+        <v>121.24022393</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2290790434342362</v>
+        <v>0.2311129257848577</v>
       </c>
       <c r="T27">
-        <v>1.277902601852361</v>
+        <v>1.292083729705386</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.63121295904422</v>
+        <v>13.10693553754252</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1811590150807947</v>
+        <v>0.1810769975859123</v>
       </c>
       <c r="C28">
-        <v>746.5249453197257</v>
+        <v>738.5721167340129</v>
       </c>
       <c r="D28">
-        <v>813.4209453197257</v>
+        <v>813.914116734013</v>
       </c>
       <c r="E28">
-        <v>-259.204</v>
+        <v>-250.758</v>
       </c>
       <c r="F28">
-        <v>219.596</v>
+        <v>228.042</v>
       </c>
       <c r="G28">
         <v>152.7</v>
@@ -3589,45 +3589,45 @@
         <v>144.775</v>
       </c>
       <c r="M28">
-        <v>11.0456788</v>
+        <v>11.8125756</v>
       </c>
       <c r="N28">
-        <v>133.7293212</v>
+        <v>132.9624244</v>
       </c>
       <c r="O28">
-        <v>30.08909727</v>
+        <v>29.91654548999999</v>
       </c>
       <c r="P28">
-        <v>103.64022393</v>
+        <v>103.04587891</v>
       </c>
       <c r="Q28">
-        <v>121.24022393</v>
+        <v>120.64587891</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2311129257848577</v>
+        <v>0.2332025309396059</v>
       </c>
       <c r="T28">
-        <v>1.292083729705386</v>
+        <v>1.306653381609178</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.225</v>
       </c>
       <c r="W28">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.10693553754252</v>
+        <v>12.25600621764486</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1810769975859123</v>
+        <v>0.1806927300910299</v>
       </c>
       <c r="C29">
-        <v>738.5721167340129</v>
+        <v>732.444705278227</v>
       </c>
       <c r="D29">
-        <v>813.914116734013</v>
+        <v>816.2327052782271</v>
       </c>
       <c r="E29">
-        <v>-250.758</v>
+        <v>-242.312</v>
       </c>
       <c r="F29">
-        <v>228.042</v>
+        <v>236.488</v>
       </c>
       <c r="G29">
         <v>152.7</v>
@@ -3671,28 +3671,28 @@
         <v>144.775</v>
       </c>
       <c r="M29">
-        <v>11.8125756</v>
+        <v>12.2500784</v>
       </c>
       <c r="N29">
-        <v>132.9624244</v>
+        <v>132.5249216</v>
       </c>
       <c r="O29">
-        <v>29.91654548999999</v>
+        <v>29.81810736</v>
       </c>
       <c r="P29">
-        <v>103.04587891</v>
+        <v>102.70681424</v>
       </c>
       <c r="Q29">
-        <v>120.64587891</v>
+        <v>120.30681424</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2332025309396059</v>
+        <v>0.235350180681986</v>
       </c>
       <c r="T29">
-        <v>1.306653381609178</v>
+        <v>1.321627746065853</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.25600621764486</v>
+        <v>11.81829170987183</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1806927300910299</v>
+        <v>0.1803084625961475</v>
       </c>
       <c r="C30">
-        <v>732.444705278227</v>
+        <v>726.3305414381573</v>
       </c>
       <c r="D30">
-        <v>816.2327052782271</v>
+        <v>818.5645414381573</v>
       </c>
       <c r="E30">
-        <v>-242.312</v>
+        <v>-233.866</v>
       </c>
       <c r="F30">
-        <v>236.488</v>
+        <v>244.934</v>
       </c>
       <c r="G30">
         <v>152.7</v>
@@ -3753,28 +3753,28 @@
         <v>144.775</v>
       </c>
       <c r="M30">
-        <v>12.2500784</v>
+        <v>12.6875812</v>
       </c>
       <c r="N30">
-        <v>132.5249216</v>
+        <v>132.0874188</v>
       </c>
       <c r="O30">
-        <v>29.81810736</v>
+        <v>29.71966922999999</v>
       </c>
       <c r="P30">
-        <v>102.70681424</v>
+        <v>102.36774957</v>
       </c>
       <c r="Q30">
-        <v>120.30681424</v>
+        <v>119.96774957</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.235350180681986</v>
+        <v>0.2375583276002078</v>
       </c>
       <c r="T30">
-        <v>1.321627746065853</v>
+        <v>1.337023923605815</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.81829170987183</v>
+        <v>11.41076440953142</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1803084625961475</v>
+        <v>0.1799241951012651</v>
       </c>
       <c r="C31">
-        <v>726.3305414381578</v>
+        <v>720.2297390775583</v>
       </c>
       <c r="D31">
-        <v>818.5645414381578</v>
+        <v>820.9097390775582</v>
       </c>
       <c r="E31">
-        <v>-233.866</v>
+        <v>-225.42</v>
       </c>
       <c r="F31">
-        <v>244.934</v>
+        <v>253.38</v>
       </c>
       <c r="G31">
         <v>152.7</v>
@@ -3835,28 +3835,28 @@
         <v>144.775</v>
       </c>
       <c r="M31">
-        <v>12.6875812</v>
+        <v>13.125084</v>
       </c>
       <c r="N31">
-        <v>132.0874188</v>
+        <v>131.649916</v>
       </c>
       <c r="O31">
-        <v>29.71966922999999</v>
+        <v>29.6212311</v>
       </c>
       <c r="P31">
-        <v>102.36774957</v>
+        <v>102.0286849</v>
       </c>
       <c r="Q31">
-        <v>119.96774957</v>
+        <v>119.6286849</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2375583276002077</v>
+        <v>0.2398295644303787</v>
       </c>
       <c r="T31">
-        <v>1.337023923605815</v>
+        <v>1.352859991932633</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.41076440953142</v>
+        <v>11.03040559588038</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1799241951012651</v>
+        <v>0.1795399276063827</v>
       </c>
       <c r="C32">
-        <v>720.2297390775583</v>
+        <v>714.1424133688167</v>
       </c>
       <c r="D32">
-        <v>820.9097390775582</v>
+        <v>823.2684133688167</v>
       </c>
       <c r="E32">
-        <v>-225.42</v>
+        <v>-216.974</v>
       </c>
       <c r="F32">
-        <v>253.38</v>
+        <v>261.826</v>
       </c>
       <c r="G32">
         <v>152.7</v>
@@ -3917,28 +3917,28 @@
         <v>144.775</v>
       </c>
       <c r="M32">
-        <v>13.125084</v>
+        <v>13.5625868</v>
       </c>
       <c r="N32">
-        <v>131.649916</v>
+        <v>131.2124132</v>
       </c>
       <c r="O32">
-        <v>29.6212311</v>
+        <v>29.52279297</v>
       </c>
       <c r="P32">
-        <v>102.0286849</v>
+        <v>101.68962023</v>
       </c>
       <c r="Q32">
-        <v>119.6286849</v>
+        <v>119.28962023</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2398295644303787</v>
+        <v>0.2421666342121488</v>
       </c>
       <c r="T32">
-        <v>1.352859991932633</v>
+        <v>1.369155076732691</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.03040559588038</v>
+        <v>10.6745860605294</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1795399276063827</v>
+        <v>0.1791556601115002</v>
       </c>
       <c r="C33">
-        <v>714.1424133688167</v>
+        <v>708.0686808118073</v>
       </c>
       <c r="D33">
-        <v>823.2684133688167</v>
+        <v>825.6406808118073</v>
       </c>
       <c r="E33">
-        <v>-216.974</v>
+        <v>-208.528</v>
       </c>
       <c r="F33">
-        <v>261.826</v>
+        <v>270.272</v>
       </c>
       <c r="G33">
         <v>152.7</v>
@@ -3999,28 +3999,28 @@
         <v>144.775</v>
       </c>
       <c r="M33">
-        <v>13.5625868</v>
+        <v>14.0000896</v>
       </c>
       <c r="N33">
-        <v>131.2124132</v>
+        <v>130.7749104</v>
       </c>
       <c r="O33">
-        <v>29.52279297</v>
+        <v>29.42435484</v>
       </c>
       <c r="P33">
-        <v>101.68962023</v>
+        <v>101.35055556</v>
       </c>
       <c r="Q33">
-        <v>119.28962023</v>
+        <v>118.95055556</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2421666342121488</v>
+        <v>0.2445724413404416</v>
       </c>
       <c r="T33">
-        <v>1.369155076732691</v>
+        <v>1.385929428732752</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.6745860605294</v>
+        <v>10.34100524613785</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1791556601115002</v>
+        <v>0.1787713926166179</v>
       </c>
       <c r="C34">
-        <v>708.0686808118073</v>
+        <v>702.0086592530745</v>
       </c>
       <c r="D34">
-        <v>825.6406808118073</v>
+        <v>828.0266592530745</v>
       </c>
       <c r="E34">
-        <v>-208.528</v>
+        <v>-200.082</v>
       </c>
       <c r="F34">
-        <v>270.272</v>
+        <v>278.718</v>
       </c>
       <c r="G34">
         <v>152.7</v>
@@ -4081,28 +4081,28 @@
         <v>144.775</v>
       </c>
       <c r="M34">
-        <v>14.0000896</v>
+        <v>14.4375924</v>
       </c>
       <c r="N34">
-        <v>130.7749104</v>
+        <v>130.3374076</v>
       </c>
       <c r="O34">
-        <v>29.42435484</v>
+        <v>29.32591670999999</v>
       </c>
       <c r="P34">
-        <v>101.35055556</v>
+        <v>101.01149089</v>
       </c>
       <c r="Q34">
-        <v>118.95055556</v>
+        <v>118.61149089</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2445724413404416</v>
+        <v>0.2470500636068924</v>
       </c>
       <c r="T34">
-        <v>1.385929428732752</v>
+        <v>1.403204507658188</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.34100524613785</v>
+        <v>10.02764145080034</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1787713926166179</v>
+        <v>0.1788350751217354</v>
       </c>
       <c r="C35">
-        <v>702.0086592530745</v>
+        <v>693.1662915138365</v>
       </c>
       <c r="D35">
-        <v>828.0266592530745</v>
+        <v>827.6302915138366</v>
       </c>
       <c r="E35">
-        <v>-200.082</v>
+        <v>-191.636</v>
       </c>
       <c r="F35">
-        <v>278.718</v>
+        <v>287.164</v>
       </c>
       <c r="G35">
         <v>152.7</v>
@@ -4163,45 +4163,45 @@
         <v>144.775</v>
       </c>
       <c r="M35">
-        <v>14.4375924</v>
+        <v>15.363274</v>
       </c>
       <c r="N35">
-        <v>130.3374076</v>
+        <v>129.411726</v>
       </c>
       <c r="O35">
-        <v>29.32591670999999</v>
+        <v>29.11763835</v>
       </c>
       <c r="P35">
-        <v>101.01149089</v>
+        <v>100.29408765</v>
       </c>
       <c r="Q35">
-        <v>118.61149089</v>
+        <v>117.89408765</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2470500636068924</v>
+        <v>0.2496027653359628</v>
       </c>
       <c r="T35">
-        <v>1.403204507658188</v>
+        <v>1.421003073823788</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.225</v>
       </c>
       <c r="W35">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.02764145080034</v>
+        <v>9.423447111598737</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1788350751217354</v>
+        <v>0.178463982626853</v>
       </c>
       <c r="C36">
-        <v>693.1662915138365</v>
+        <v>687.0353689269881</v>
       </c>
       <c r="D36">
-        <v>827.6302915138366</v>
+        <v>829.9453689269881</v>
       </c>
       <c r="E36">
-        <v>-191.636</v>
+        <v>-183.19</v>
       </c>
       <c r="F36">
-        <v>287.164</v>
+        <v>295.61</v>
       </c>
       <c r="G36">
         <v>152.7</v>
@@ -4245,28 +4245,28 @@
         <v>144.775</v>
       </c>
       <c r="M36">
-        <v>15.363274</v>
+        <v>15.815135</v>
       </c>
       <c r="N36">
-        <v>129.411726</v>
+        <v>128.959865</v>
       </c>
       <c r="O36">
-        <v>29.11763835</v>
+        <v>29.015969625</v>
       </c>
       <c r="P36">
-        <v>100.29408765</v>
+        <v>99.94389537499998</v>
       </c>
       <c r="Q36">
-        <v>117.89408765</v>
+        <v>117.543895375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2496027653359628</v>
+        <v>0.25223401173362</v>
       </c>
       <c r="T36">
-        <v>1.421003073823788</v>
+        <v>1.439349288179099</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.423447111598737</v>
+        <v>9.154205765553058</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.178463982626853</v>
+        <v>0.1780928901319706</v>
       </c>
       <c r="C37">
-        <v>687.0353689269881</v>
+        <v>680.9174343072511</v>
       </c>
       <c r="D37">
-        <v>829.9453689269881</v>
+        <v>832.2734343072513</v>
       </c>
       <c r="E37">
-        <v>-183.19</v>
+        <v>-174.744</v>
       </c>
       <c r="F37">
-        <v>295.61</v>
+        <v>304.056</v>
       </c>
       <c r="G37">
         <v>152.7</v>
@@ -4327,28 +4327,28 @@
         <v>144.775</v>
       </c>
       <c r="M37">
-        <v>15.815135</v>
+        <v>16.266996</v>
       </c>
       <c r="N37">
-        <v>128.959865</v>
+        <v>128.508004</v>
       </c>
       <c r="O37">
-        <v>29.015969625</v>
+        <v>28.91430089999999</v>
       </c>
       <c r="P37">
-        <v>99.94389537499998</v>
+        <v>99.59370309999997</v>
       </c>
       <c r="Q37">
-        <v>117.543895375</v>
+        <v>117.1937031</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.25223401173362</v>
+        <v>0.2549474845812041</v>
       </c>
       <c r="T37">
-        <v>1.439349288179099</v>
+        <v>1.458268821733014</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.154205765553058</v>
+        <v>8.899922272065472</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1780928901319706</v>
+        <v>0.1777217976370883</v>
       </c>
       <c r="C38">
-        <v>680.9174343072509</v>
+        <v>674.8125972590406</v>
       </c>
       <c r="D38">
-        <v>832.273434307251</v>
+        <v>834.6145972590405</v>
       </c>
       <c r="E38">
-        <v>-174.744</v>
+        <v>-166.298</v>
       </c>
       <c r="F38">
-        <v>304.056</v>
+        <v>312.502</v>
       </c>
       <c r="G38">
         <v>152.7</v>
@@ -4409,28 +4409,28 @@
         <v>144.775</v>
       </c>
       <c r="M38">
-        <v>16.266996</v>
+        <v>16.718857</v>
       </c>
       <c r="N38">
-        <v>128.508004</v>
+        <v>128.056143</v>
       </c>
       <c r="O38">
-        <v>28.91430089999999</v>
+        <v>28.81263217499999</v>
       </c>
       <c r="P38">
-        <v>99.59370309999997</v>
+        <v>99.24351082499997</v>
       </c>
       <c r="Q38">
-        <v>117.1937031</v>
+        <v>116.843510825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2549474845812041</v>
+        <v>0.2577470994239496</v>
       </c>
       <c r="T38">
-        <v>1.458268821733014</v>
+        <v>1.477788975399751</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.899922272065474</v>
+        <v>8.65938383227992</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1777217976370883</v>
+        <v>0.1773507051422058</v>
       </c>
       <c r="C39">
-        <v>674.8125972590406</v>
+        <v>668.7209686235067</v>
       </c>
       <c r="D39">
-        <v>834.6145972590405</v>
+        <v>836.9689686235068</v>
       </c>
       <c r="E39">
-        <v>-166.298</v>
+        <v>-157.852</v>
       </c>
       <c r="F39">
-        <v>312.502</v>
+        <v>320.948</v>
       </c>
       <c r="G39">
         <v>152.7</v>
@@ -4491,28 +4491,28 @@
         <v>144.775</v>
       </c>
       <c r="M39">
-        <v>16.718857</v>
+        <v>17.170718</v>
       </c>
       <c r="N39">
-        <v>128.056143</v>
+        <v>127.604282</v>
       </c>
       <c r="O39">
-        <v>28.81263217499999</v>
+        <v>28.71096345</v>
       </c>
       <c r="P39">
-        <v>99.24351082499997</v>
+        <v>98.89331854999999</v>
       </c>
       <c r="Q39">
-        <v>116.843510825</v>
+        <v>116.49331855</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2577470994239496</v>
+        <v>0.2606370244229126</v>
       </c>
       <c r="T39">
-        <v>1.477788975399751</v>
+        <v>1.497938811442834</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.65938383227992</v>
+        <v>8.431505310377817</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1773507051422058</v>
+        <v>0.1769796126473234</v>
       </c>
       <c r="C40">
-        <v>668.7209686235067</v>
+        <v>662.6426604960288</v>
       </c>
       <c r="D40">
-        <v>836.9689686235068</v>
+        <v>839.3366604960289</v>
       </c>
       <c r="E40">
-        <v>-157.852</v>
+        <v>-149.406</v>
       </c>
       <c r="F40">
-        <v>320.948</v>
+        <v>329.394</v>
       </c>
       <c r="G40">
         <v>152.7</v>
@@ -4573,28 +4573,28 @@
         <v>144.775</v>
       </c>
       <c r="M40">
-        <v>17.170718</v>
+        <v>17.622579</v>
       </c>
       <c r="N40">
-        <v>127.604282</v>
+        <v>127.152421</v>
       </c>
       <c r="O40">
-        <v>28.71096345</v>
+        <v>28.60929472499999</v>
       </c>
       <c r="P40">
-        <v>98.89331854999999</v>
+        <v>98.54312627499998</v>
       </c>
       <c r="Q40">
-        <v>116.49331855</v>
+        <v>116.143126275</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2606370244229126</v>
+        <v>0.2636217010611859</v>
       </c>
       <c r="T40">
-        <v>1.497938811442834</v>
+        <v>1.518749297847986</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.431505310377817</v>
+        <v>8.215312866521977</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1769796126473234</v>
+        <v>0.1766085201524409</v>
       </c>
       <c r="C41">
-        <v>662.6426604960288</v>
+        <v>656.577786244006</v>
       </c>
       <c r="D41">
-        <v>839.3366604960289</v>
+        <v>841.7177862440061</v>
       </c>
       <c r="E41">
-        <v>-149.406</v>
+        <v>-140.96</v>
       </c>
       <c r="F41">
-        <v>329.394</v>
+        <v>337.84</v>
       </c>
       <c r="G41">
         <v>152.7</v>
@@ -4655,28 +4655,28 @@
         <v>144.775</v>
       </c>
       <c r="M41">
-        <v>17.622579</v>
+        <v>18.07444</v>
       </c>
       <c r="N41">
-        <v>127.152421</v>
+        <v>126.70056</v>
       </c>
       <c r="O41">
-        <v>28.60929472499999</v>
+        <v>28.50762599999999</v>
       </c>
       <c r="P41">
-        <v>98.54312627499998</v>
+        <v>98.19293399999998</v>
       </c>
       <c r="Q41">
-        <v>116.143126275</v>
+        <v>115.792934</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2636217010611859</v>
+        <v>0.2667058669207349</v>
       </c>
       <c r="T41">
-        <v>1.518749297847986</v>
+        <v>1.54025346713331</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.215312866521977</v>
+        <v>8.009930044858926</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1766085201524409</v>
+        <v>0.1762374276575586</v>
       </c>
       <c r="C42">
-        <v>656.577786244006</v>
+        <v>650.5264605249508</v>
       </c>
       <c r="D42">
-        <v>841.7177862440061</v>
+        <v>844.112460524951</v>
       </c>
       <c r="E42">
-        <v>-140.96</v>
+        <v>-132.514</v>
       </c>
       <c r="F42">
-        <v>337.84</v>
+        <v>346.2860000000001</v>
       </c>
       <c r="G42">
         <v>152.7</v>
@@ -4737,28 +4737,28 @@
         <v>144.775</v>
       </c>
       <c r="M42">
-        <v>18.07444</v>
+        <v>18.526301</v>
       </c>
       <c r="N42">
-        <v>126.70056</v>
+        <v>126.248699</v>
       </c>
       <c r="O42">
-        <v>28.50762599999999</v>
+        <v>28.405957275</v>
       </c>
       <c r="P42">
-        <v>98.19293399999998</v>
+        <v>97.84274172499998</v>
       </c>
       <c r="Q42">
-        <v>115.792934</v>
+        <v>115.442741725</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2667058669207349</v>
+        <v>0.269894580775523</v>
       </c>
       <c r="T42">
-        <v>1.54025346713331</v>
+        <v>1.562486591309661</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.009930044858926</v>
+        <v>7.814565897423342</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1762374276575586</v>
+        <v>0.1758663351626761</v>
       </c>
       <c r="C43">
-        <v>650.5264605249508</v>
+        <v>644.4887993048956</v>
       </c>
       <c r="D43">
-        <v>844.112460524951</v>
+        <v>846.5207993048956</v>
       </c>
       <c r="E43">
-        <v>-132.514</v>
+        <v>-124.068</v>
       </c>
       <c r="F43">
-        <v>346.2860000000001</v>
+        <v>354.732</v>
       </c>
       <c r="G43">
         <v>152.7</v>
@@ -4819,28 +4819,28 @@
         <v>144.775</v>
       </c>
       <c r="M43">
-        <v>18.526301</v>
+        <v>18.978162</v>
       </c>
       <c r="N43">
-        <v>126.248699</v>
+        <v>125.796838</v>
       </c>
       <c r="O43">
-        <v>28.405957275</v>
+        <v>28.30428855</v>
       </c>
       <c r="P43">
-        <v>97.84274172499998</v>
+        <v>97.49254944999998</v>
       </c>
       <c r="Q43">
-        <v>115.442741725</v>
+        <v>115.09254945</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.269894580775523</v>
+        <v>0.2731932502804761</v>
       </c>
       <c r="T43">
-        <v>1.562486591309661</v>
+        <v>1.58548637494037</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.814565897423342</v>
+        <v>7.628504804627549</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1758663351626762</v>
+        <v>0.1757618426677938</v>
       </c>
       <c r="C44">
-        <v>644.4887993048953</v>
+        <v>636.7234226976806</v>
       </c>
       <c r="D44">
-        <v>846.5207993048954</v>
+        <v>847.2014226976806</v>
       </c>
       <c r="E44">
-        <v>-124.068</v>
+        <v>-115.622</v>
       </c>
       <c r="F44">
-        <v>354.732</v>
+        <v>363.178</v>
       </c>
       <c r="G44">
         <v>152.7</v>
@@ -4901,45 +4901,45 @@
         <v>144.775</v>
       </c>
       <c r="M44">
-        <v>18.978162</v>
+        <v>19.7205654</v>
       </c>
       <c r="N44">
-        <v>125.796838</v>
+        <v>125.0544346</v>
       </c>
       <c r="O44">
-        <v>28.30428855</v>
+        <v>28.137247785</v>
       </c>
       <c r="P44">
-        <v>97.49254944999998</v>
+        <v>96.91718681499998</v>
       </c>
       <c r="Q44">
-        <v>115.09254945</v>
+        <v>114.517186815</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2731932502804761</v>
+        <v>0.2766076625750768</v>
       </c>
       <c r="T44">
-        <v>1.58548637494037</v>
+        <v>1.609293168523033</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.225</v>
       </c>
       <c r="W44">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.62850480462755</v>
+        <v>7.341320954215642</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1757618426677938</v>
+        <v>0.1753969501729113</v>
       </c>
       <c r="C45">
-        <v>636.7234226976806</v>
+        <v>630.6627985910459</v>
       </c>
       <c r="D45">
-        <v>847.2014226976806</v>
+        <v>849.5867985910459</v>
       </c>
       <c r="E45">
-        <v>-115.622</v>
+        <v>-107.176</v>
       </c>
       <c r="F45">
-        <v>363.178</v>
+        <v>371.624</v>
       </c>
       <c r="G45">
         <v>152.7</v>
@@ -4983,28 +4983,28 @@
         <v>144.775</v>
       </c>
       <c r="M45">
-        <v>19.7205654</v>
+        <v>20.1791832</v>
       </c>
       <c r="N45">
-        <v>125.0544346</v>
+        <v>124.5958168</v>
       </c>
       <c r="O45">
-        <v>28.137247785</v>
+        <v>28.03405878</v>
       </c>
       <c r="P45">
-        <v>96.91718681499998</v>
+        <v>96.56175801999998</v>
       </c>
       <c r="Q45">
-        <v>114.517186815</v>
+        <v>114.16175802</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2766076625750768</v>
+        <v>0.2801440181659131</v>
       </c>
       <c r="T45">
-        <v>1.609293168523033</v>
+        <v>1.633950204733648</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.341320954215642</v>
+        <v>7.174472750710741</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1753969501729113</v>
+        <v>0.175032057678029</v>
       </c>
       <c r="C46">
-        <v>630.6627985910459</v>
+        <v>624.6156449154571</v>
       </c>
       <c r="D46">
-        <v>849.5867985910459</v>
+        <v>851.9856449154571</v>
       </c>
       <c r="E46">
-        <v>-107.176</v>
+        <v>-98.73000000000002</v>
       </c>
       <c r="F46">
-        <v>371.624</v>
+        <v>380.07</v>
       </c>
       <c r="G46">
         <v>152.7</v>
@@ -5065,28 +5065,28 @@
         <v>144.775</v>
       </c>
       <c r="M46">
-        <v>20.1791832</v>
+        <v>20.637801</v>
       </c>
       <c r="N46">
-        <v>124.5958168</v>
+        <v>124.137199</v>
       </c>
       <c r="O46">
-        <v>28.03405878</v>
+        <v>27.930869775</v>
       </c>
       <c r="P46">
-        <v>96.56175801999998</v>
+        <v>96.20632922499999</v>
       </c>
       <c r="Q46">
-        <v>114.16175802</v>
+        <v>113.806329225</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2801440181659131</v>
+        <v>0.2838089685055072</v>
       </c>
       <c r="T46">
-        <v>1.633950204733648</v>
+        <v>1.659503860442832</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.174472750710741</v>
+        <v>7.015040022917169</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.175032057678029</v>
+        <v>0.1746671651831466</v>
       </c>
       <c r="C47">
-        <v>624.6156449154571</v>
+        <v>618.5820760970955</v>
       </c>
       <c r="D47">
-        <v>851.9856449154571</v>
+        <v>854.3980760970957</v>
       </c>
       <c r="E47">
-        <v>-98.73000000000002</v>
+        <v>-90.28399999999999</v>
       </c>
       <c r="F47">
-        <v>380.07</v>
+        <v>388.516</v>
       </c>
       <c r="G47">
         <v>152.7</v>
@@ -5147,28 +5147,28 @@
         <v>144.775</v>
       </c>
       <c r="M47">
-        <v>20.637801</v>
+        <v>21.0964188</v>
       </c>
       <c r="N47">
-        <v>124.137199</v>
+        <v>123.6785812</v>
       </c>
       <c r="O47">
-        <v>27.930869775</v>
+        <v>27.82768076999999</v>
       </c>
       <c r="P47">
-        <v>96.20632922499999</v>
+        <v>95.85090042999997</v>
       </c>
       <c r="Q47">
-        <v>113.806329225</v>
+        <v>113.45090043</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2838089685055072</v>
+        <v>0.2876096577465677</v>
       </c>
       <c r="T47">
-        <v>1.659503860442832</v>
+        <v>1.686003947844948</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.015040022917169</v>
+        <v>6.862539152853752</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1746671651831466</v>
+        <v>0.1743022726882641</v>
       </c>
       <c r="C48">
-        <v>618.5820760970955</v>
+        <v>612.5622078618321</v>
       </c>
       <c r="D48">
-        <v>854.3980760970957</v>
+        <v>856.8242078618321</v>
       </c>
       <c r="E48">
-        <v>-90.28399999999999</v>
+        <v>-81.83799999999997</v>
       </c>
       <c r="F48">
-        <v>388.516</v>
+        <v>396.962</v>
       </c>
       <c r="G48">
         <v>152.7</v>
@@ -5229,28 +5229,28 @@
         <v>144.775</v>
       </c>
       <c r="M48">
-        <v>21.0964188</v>
+        <v>21.5550366</v>
       </c>
       <c r="N48">
-        <v>123.6785812</v>
+        <v>123.2199634</v>
       </c>
       <c r="O48">
-        <v>27.82768076999999</v>
+        <v>27.72449176499999</v>
       </c>
       <c r="P48">
-        <v>95.85090042999997</v>
+        <v>95.49547163499997</v>
       </c>
       <c r="Q48">
-        <v>113.45090043</v>
+        <v>113.095471635</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2876096577465677</v>
+        <v>0.2915537692231399</v>
       </c>
       <c r="T48">
-        <v>1.686003947844948</v>
+        <v>1.713504038545257</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.862539152853752</v>
+        <v>6.716527681516437</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1743022726882641</v>
+        <v>0.1739373801933817</v>
       </c>
       <c r="C49">
-        <v>612.5622078618321</v>
+        <v>606.5561572537307</v>
       </c>
       <c r="D49">
-        <v>856.8242078618321</v>
+        <v>859.2641572537308</v>
       </c>
       <c r="E49">
-        <v>-81.83799999999997</v>
+        <v>-73.392</v>
       </c>
       <c r="F49">
-        <v>396.962</v>
+        <v>405.408</v>
       </c>
       <c r="G49">
         <v>152.7</v>
@@ -5311,28 +5311,28 @@
         <v>144.775</v>
       </c>
       <c r="M49">
-        <v>21.5550366</v>
+        <v>22.0136544</v>
       </c>
       <c r="N49">
-        <v>123.2199634</v>
+        <v>122.7613456</v>
       </c>
       <c r="O49">
-        <v>27.72449176499999</v>
+        <v>27.62130276</v>
       </c>
       <c r="P49">
-        <v>95.49547163499997</v>
+        <v>95.14004283999998</v>
       </c>
       <c r="Q49">
-        <v>113.095471635</v>
+        <v>112.74004284</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2915537692231399</v>
+        <v>0.2956495772949648</v>
       </c>
       <c r="T49">
-        <v>1.713504038545257</v>
+        <v>1.742061825041732</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.716527681516437</v>
+        <v>6.576600021484846</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1739373801933817</v>
+        <v>0.1735724876984993</v>
       </c>
       <c r="C50">
-        <v>606.5561572537307</v>
+        <v>600.5640426538741</v>
       </c>
       <c r="D50">
-        <v>859.2641572537308</v>
+        <v>861.7180426538741</v>
       </c>
       <c r="E50">
-        <v>-73.392</v>
+        <v>-64.94600000000003</v>
       </c>
       <c r="F50">
-        <v>405.408</v>
+        <v>413.854</v>
       </c>
       <c r="G50">
         <v>152.7</v>
@@ -5393,28 +5393,28 @@
         <v>144.775</v>
       </c>
       <c r="M50">
-        <v>22.0136544</v>
+        <v>22.4722722</v>
       </c>
       <c r="N50">
-        <v>122.7613456</v>
+        <v>122.3027278</v>
       </c>
       <c r="O50">
-        <v>27.62130276</v>
+        <v>27.518113755</v>
       </c>
       <c r="P50">
-        <v>95.14004283999998</v>
+        <v>94.78461404499998</v>
       </c>
       <c r="Q50">
-        <v>112.74004284</v>
+        <v>112.384614045</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2956495772949648</v>
+        <v>0.2999060052911751</v>
       </c>
       <c r="T50">
-        <v>1.742061825041732</v>
+        <v>1.771739524734147</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.576600021484846</v>
+        <v>6.442383694515768</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1735724876984993</v>
+        <v>0.1732075952036169</v>
       </c>
       <c r="C51">
-        <v>600.5640426538741</v>
+        <v>594.5859837995072</v>
       </c>
       <c r="D51">
-        <v>861.7180426538741</v>
+        <v>864.1859837995072</v>
       </c>
       <c r="E51">
-        <v>-64.94600000000003</v>
+        <v>-56.5</v>
       </c>
       <c r="F51">
-        <v>413.854</v>
+        <v>422.3</v>
       </c>
       <c r="G51">
         <v>152.7</v>
@@ -5475,28 +5475,28 @@
         <v>144.775</v>
       </c>
       <c r="M51">
-        <v>22.4722722</v>
+        <v>22.93089</v>
       </c>
       <c r="N51">
-        <v>122.3027278</v>
+        <v>121.84411</v>
       </c>
       <c r="O51">
-        <v>27.518113755</v>
+        <v>27.41492474999999</v>
       </c>
       <c r="P51">
-        <v>94.78461404499998</v>
+        <v>94.42918524999997</v>
       </c>
       <c r="Q51">
-        <v>112.384614045</v>
+        <v>112.02918525</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2999060052911751</v>
+        <v>0.3043326904072338</v>
       </c>
       <c r="T51">
-        <v>1.771739524734147</v>
+        <v>1.802604332414258</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.442383694515768</v>
+        <v>6.313536020625452</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1732075952036169</v>
+        <v>0.1728427027087345</v>
       </c>
       <c r="C52">
-        <v>594.5859837995072</v>
+        <v>588.6221018035135</v>
       </c>
       <c r="D52">
-        <v>864.1859837995072</v>
+        <v>866.6681018035137</v>
       </c>
       <c r="E52">
-        <v>-56.5</v>
+        <v>-48.05399999999997</v>
       </c>
       <c r="F52">
-        <v>422.3</v>
+        <v>430.746</v>
       </c>
       <c r="G52">
         <v>152.7</v>
@@ -5557,28 +5557,28 @@
         <v>144.775</v>
       </c>
       <c r="M52">
-        <v>22.93089</v>
+        <v>23.3895078</v>
       </c>
       <c r="N52">
-        <v>121.84411</v>
+        <v>121.3854922</v>
       </c>
       <c r="O52">
-        <v>27.41492474999999</v>
+        <v>27.31173574499999</v>
       </c>
       <c r="P52">
-        <v>94.42918524999997</v>
+        <v>94.07375645499998</v>
       </c>
       <c r="Q52">
-        <v>112.02918525</v>
+        <v>111.673756455</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3043326904072338</v>
+        <v>0.3089400565484378</v>
       </c>
       <c r="T52">
-        <v>1.802604332414258</v>
+        <v>1.834728928162946</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.313536020625452</v>
+        <v>6.189741196691619</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1728427027087345</v>
+        <v>0.1728808102138521</v>
       </c>
       <c r="C53">
-        <v>588.6221018035135</v>
+        <v>579.9162155227357</v>
       </c>
       <c r="D53">
-        <v>866.6681018035137</v>
+        <v>866.4082155227358</v>
       </c>
       <c r="E53">
-        <v>-48.05399999999997</v>
+        <v>-39.608</v>
       </c>
       <c r="F53">
-        <v>430.746</v>
+        <v>439.192</v>
       </c>
       <c r="G53">
         <v>152.7</v>
@@ -5639,45 +5639,45 @@
         <v>144.775</v>
       </c>
       <c r="M53">
-        <v>23.3895078</v>
+        <v>24.2873176</v>
       </c>
       <c r="N53">
-        <v>121.3854922</v>
+        <v>120.4876824</v>
       </c>
       <c r="O53">
-        <v>27.31173574499999</v>
+        <v>27.10972854</v>
       </c>
       <c r="P53">
-        <v>94.07375645499998</v>
+        <v>93.37795385999999</v>
       </c>
       <c r="Q53">
-        <v>111.673756455</v>
+        <v>110.97795386</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3089400565484378</v>
+        <v>0.3137393962788586</v>
       </c>
       <c r="T53">
-        <v>1.834728928162946</v>
+        <v>1.868192048734496</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.225</v>
       </c>
       <c r="W53">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.189741196691619</v>
+        <v>5.960929995826298</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1728808102138521</v>
+        <v>0.1725236677189697</v>
       </c>
       <c r="C54">
-        <v>579.9162155227357</v>
+        <v>573.9119945309366</v>
       </c>
       <c r="D54">
-        <v>866.4082155227358</v>
+        <v>868.8499945309366</v>
       </c>
       <c r="E54">
-        <v>-39.608</v>
+        <v>-31.16199999999998</v>
       </c>
       <c r="F54">
-        <v>439.192</v>
+        <v>447.638</v>
       </c>
       <c r="G54">
         <v>152.7</v>
@@ -5721,28 +5721,28 @@
         <v>144.775</v>
       </c>
       <c r="M54">
-        <v>24.2873176</v>
+        <v>24.7543814</v>
       </c>
       <c r="N54">
-        <v>120.4876824</v>
+        <v>120.0206186</v>
       </c>
       <c r="O54">
-        <v>27.10972854</v>
+        <v>27.00463918499999</v>
       </c>
       <c r="P54">
-        <v>93.37795385999999</v>
+        <v>93.01597941499998</v>
       </c>
       <c r="Q54">
-        <v>110.97795386</v>
+        <v>110.615979415</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3137393962788586</v>
+        <v>0.3187429632318504</v>
       </c>
       <c r="T54">
-        <v>1.868192048734496</v>
+        <v>1.903079131883558</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.960929995826298</v>
+        <v>5.848459618546556</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1725236677189697</v>
+        <v>0.1721665252240873</v>
       </c>
       <c r="C55">
-        <v>573.9119945309366</v>
+        <v>567.9215756603146</v>
       </c>
       <c r="D55">
-        <v>868.8499945309366</v>
+        <v>871.3055756603146</v>
       </c>
       <c r="E55">
-        <v>-31.16199999999998</v>
+        <v>-22.71599999999995</v>
       </c>
       <c r="F55">
-        <v>447.638</v>
+        <v>456.0840000000001</v>
       </c>
       <c r="G55">
         <v>152.7</v>
@@ -5803,28 +5803,28 @@
         <v>144.775</v>
       </c>
       <c r="M55">
-        <v>24.7543814</v>
+        <v>25.22144520000001</v>
       </c>
       <c r="N55">
-        <v>120.0206186</v>
+        <v>119.5535548</v>
       </c>
       <c r="O55">
-        <v>27.00463918499999</v>
+        <v>26.89954982999999</v>
       </c>
       <c r="P55">
-        <v>93.01597941499998</v>
+        <v>92.65400496999997</v>
       </c>
       <c r="Q55">
-        <v>110.615979415</v>
+        <v>110.25400497</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3187429632318504</v>
+        <v>0.3239640765741028</v>
       </c>
       <c r="T55">
-        <v>1.903079131883558</v>
+        <v>1.939483044734753</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.848459618546556</v>
+        <v>5.740154810795693</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1721665252240873</v>
+        <v>0.1718093827292049</v>
       </c>
       <c r="C56">
-        <v>567.9215756603146</v>
+        <v>561.9450762669878</v>
       </c>
       <c r="D56">
-        <v>871.3055756603146</v>
+        <v>873.7750762669879</v>
       </c>
       <c r="E56">
-        <v>-22.71599999999995</v>
+        <v>-14.26999999999998</v>
       </c>
       <c r="F56">
-        <v>456.0840000000001</v>
+        <v>464.53</v>
       </c>
       <c r="G56">
         <v>152.7</v>
@@ -5885,28 +5885,28 @@
         <v>144.775</v>
       </c>
       <c r="M56">
-        <v>25.22144520000001</v>
+        <v>25.688509</v>
       </c>
       <c r="N56">
-        <v>119.5535548</v>
+        <v>119.086491</v>
       </c>
       <c r="O56">
-        <v>26.89954982999999</v>
+        <v>26.79446047499999</v>
       </c>
       <c r="P56">
-        <v>92.65400496999997</v>
+        <v>92.29203052499997</v>
       </c>
       <c r="Q56">
-        <v>110.25400497</v>
+        <v>109.892030525</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3239640765741028</v>
+        <v>0.329417239398233</v>
       </c>
       <c r="T56">
-        <v>1.939483044734753</v>
+        <v>1.977504909268224</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.740154810795693</v>
+        <v>5.635788359690317</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1718093827292049</v>
+        <v>0.1714522402343224</v>
       </c>
       <c r="C57">
-        <v>561.9450762669878</v>
+        <v>555.9826150413235</v>
       </c>
       <c r="D57">
-        <v>873.7750762669879</v>
+        <v>876.2586150413237</v>
       </c>
       <c r="E57">
-        <v>-14.26999999999998</v>
+        <v>-5.823999999999955</v>
       </c>
       <c r="F57">
-        <v>464.53</v>
+        <v>472.9760000000001</v>
       </c>
       <c r="G57">
         <v>152.7</v>
@@ -5967,28 +5967,28 @@
         <v>144.775</v>
       </c>
       <c r="M57">
-        <v>25.688509</v>
+        <v>26.15557280000001</v>
       </c>
       <c r="N57">
-        <v>119.086491</v>
+        <v>118.6194272</v>
       </c>
       <c r="O57">
-        <v>26.79446047499999</v>
+        <v>26.68937111999999</v>
       </c>
       <c r="P57">
-        <v>92.29203052499997</v>
+        <v>91.93005607999999</v>
       </c>
       <c r="Q57">
-        <v>109.892030525</v>
+        <v>109.53005608</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.329417239398233</v>
+        <v>0.3351182732598237</v>
       </c>
       <c r="T57">
-        <v>1.977504909268224</v>
+        <v>2.017255040371398</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.635788359690317</v>
+        <v>5.535149281838704</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1714522402343224</v>
+        <v>0.17109509773944</v>
       </c>
       <c r="C58">
-        <v>555.9826150413235</v>
+        <v>550.0343120269538</v>
       </c>
       <c r="D58">
-        <v>876.2586150413237</v>
+        <v>878.7563120269538</v>
       </c>
       <c r="E58">
-        <v>-5.823999999999955</v>
+        <v>2.622000000000071</v>
       </c>
       <c r="F58">
-        <v>472.9760000000001</v>
+        <v>481.4220000000001</v>
       </c>
       <c r="G58">
         <v>152.7</v>
@@ -6049,28 +6049,28 @@
         <v>144.775</v>
       </c>
       <c r="M58">
-        <v>26.15557280000001</v>
+        <v>26.62263660000001</v>
       </c>
       <c r="N58">
-        <v>118.6194272</v>
+        <v>118.1523634</v>
       </c>
       <c r="O58">
-        <v>26.68937111999999</v>
+        <v>26.58428176499999</v>
       </c>
       <c r="P58">
-        <v>91.93005607999999</v>
+        <v>91.56808163499997</v>
       </c>
       <c r="Q58">
-        <v>109.53005608</v>
+        <v>109.168081635</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3351182732598237</v>
+        <v>0.3410844714870699</v>
       </c>
       <c r="T58">
-        <v>2.017255040371398</v>
+        <v>2.058854014781696</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.535149281838704</v>
+        <v>5.438041399701182</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.17109509773944</v>
+        <v>0.1707379552445576</v>
       </c>
       <c r="C59">
-        <v>550.0343120269538</v>
+        <v>544.1002886401189</v>
       </c>
       <c r="D59">
-        <v>878.7563120269538</v>
+        <v>881.268288640119</v>
       </c>
       <c r="E59">
-        <v>2.622000000000071</v>
+        <v>11.06800000000004</v>
       </c>
       <c r="F59">
-        <v>481.4220000000001</v>
+        <v>489.8680000000001</v>
       </c>
       <c r="G59">
         <v>152.7</v>
@@ -6131,28 +6131,28 @@
         <v>144.775</v>
       </c>
       <c r="M59">
-        <v>26.62263660000001</v>
+        <v>27.08970040000001</v>
       </c>
       <c r="N59">
-        <v>118.1523634</v>
+        <v>117.6852996</v>
       </c>
       <c r="O59">
-        <v>26.58428176499999</v>
+        <v>26.47919241</v>
       </c>
       <c r="P59">
-        <v>91.56808163499997</v>
+        <v>91.20610718999998</v>
       </c>
       <c r="Q59">
-        <v>109.168081635</v>
+        <v>108.80610719</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3410844714870699</v>
+        <v>0.3473347743918039</v>
       </c>
       <c r="T59">
-        <v>2.058854014781696</v>
+        <v>2.102433892735342</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.438041399701182</v>
+        <v>5.344282065223577</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1707379552445576</v>
+        <v>0.1703808127496752</v>
       </c>
       <c r="C60">
-        <v>544.1002886401188</v>
+        <v>538.1806676893394</v>
       </c>
       <c r="D60">
-        <v>881.2682886401187</v>
+        <v>883.7946676893395</v>
       </c>
       <c r="E60">
-        <v>11.06799999999998</v>
+        <v>19.51399999999995</v>
       </c>
       <c r="F60">
-        <v>489.868</v>
+        <v>498.314</v>
       </c>
       <c r="G60">
         <v>152.7</v>
@@ -6213,28 +6213,28 @@
         <v>144.775</v>
       </c>
       <c r="M60">
-        <v>27.0897004</v>
+        <v>27.5567642</v>
       </c>
       <c r="N60">
-        <v>117.6852996</v>
+        <v>117.2182358</v>
       </c>
       <c r="O60">
-        <v>26.47919241</v>
+        <v>26.374103055</v>
       </c>
       <c r="P60">
-        <v>91.20610718999998</v>
+        <v>90.84413274499998</v>
       </c>
       <c r="Q60">
-        <v>108.80610719</v>
+        <v>108.444132745</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3473347743918038</v>
+        <v>0.3538899701211591</v>
       </c>
       <c r="T60">
-        <v>2.102433892735342</v>
+        <v>2.148139618394044</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.344282065223577</v>
+        <v>5.253701013270636</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1703808127496752</v>
+        <v>0.1700236702547928</v>
       </c>
       <c r="C61">
-        <v>538.1806676893394</v>
+        <v>532.2755733954336</v>
       </c>
       <c r="D61">
-        <v>883.7946676893395</v>
+        <v>886.3355733954337</v>
       </c>
       <c r="E61">
-        <v>19.51399999999995</v>
+        <v>27.95999999999998</v>
       </c>
       <c r="F61">
-        <v>498.314</v>
+        <v>506.76</v>
       </c>
       <c r="G61">
         <v>152.7</v>
@@ -6295,28 +6295,28 @@
         <v>144.775</v>
       </c>
       <c r="M61">
-        <v>27.5567642</v>
+        <v>28.023828</v>
       </c>
       <c r="N61">
-        <v>117.2182358</v>
+        <v>116.751172</v>
       </c>
       <c r="O61">
-        <v>26.374103055</v>
+        <v>26.2690137</v>
       </c>
       <c r="P61">
-        <v>90.84413274499998</v>
+        <v>90.48215829999998</v>
       </c>
       <c r="Q61">
-        <v>108.444132745</v>
+        <v>108.0821583</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3538899701211591</v>
+        <v>0.3607729256369819</v>
       </c>
       <c r="T61">
-        <v>2.148139618394044</v>
+        <v>2.19613063033568</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.253701013270636</v>
+        <v>5.166139329716125</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1700236702547928</v>
+        <v>0.1696665277599104</v>
       </c>
       <c r="C62">
-        <v>532.2755733954336</v>
+        <v>526.3851314118739</v>
       </c>
       <c r="D62">
-        <v>886.3355733954337</v>
+        <v>888.891131411874</v>
       </c>
       <c r="E62">
-        <v>27.95999999999998</v>
+        <v>36.40600000000001</v>
       </c>
       <c r="F62">
-        <v>506.76</v>
+        <v>515.206</v>
       </c>
       <c r="G62">
         <v>152.7</v>
@@ -6377,28 +6377,28 @@
         <v>144.775</v>
       </c>
       <c r="M62">
-        <v>28.023828</v>
+        <v>28.4908918</v>
       </c>
       <c r="N62">
-        <v>116.751172</v>
+        <v>116.2841082</v>
       </c>
       <c r="O62">
-        <v>26.2690137</v>
+        <v>26.16392434499999</v>
       </c>
       <c r="P62">
-        <v>90.48215829999998</v>
+        <v>90.12018385499998</v>
       </c>
       <c r="Q62">
-        <v>108.0821583</v>
+        <v>107.720183855</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3607729256369819</v>
+        <v>0.3680088532305395</v>
       </c>
       <c r="T62">
-        <v>2.19613063033568</v>
+        <v>2.246582719812786</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.166139329716125</v>
+        <v>5.081448521032254</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1696665277599104</v>
+        <v>0.169309385265028</v>
       </c>
       <c r="C63">
-        <v>526.3851314118739</v>
+        <v>520.5094688455035</v>
       </c>
       <c r="D63">
-        <v>888.891131411874</v>
+        <v>891.4614688455036</v>
       </c>
       <c r="E63">
-        <v>36.40600000000001</v>
+        <v>44.85200000000003</v>
       </c>
       <c r="F63">
-        <v>515.206</v>
+        <v>523.652</v>
       </c>
       <c r="G63">
         <v>152.7</v>
@@ -6459,28 +6459,28 @@
         <v>144.775</v>
       </c>
       <c r="M63">
-        <v>28.4908918</v>
+        <v>28.9579556</v>
       </c>
       <c r="N63">
-        <v>116.2841082</v>
+        <v>115.8170444</v>
       </c>
       <c r="O63">
-        <v>26.16392434499999</v>
+        <v>26.05883498999999</v>
       </c>
       <c r="P63">
-        <v>90.12018385499998</v>
+        <v>89.75820940999998</v>
       </c>
       <c r="Q63">
-        <v>107.720183855</v>
+        <v>107.35820941</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3680088532305395</v>
+        <v>0.3756256191184947</v>
       </c>
       <c r="T63">
-        <v>2.246582719812786</v>
+        <v>2.299690182420266</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.081448521032254</v>
+        <v>4.999489673918831</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.169309385265028</v>
+        <v>0.1689522427701456</v>
       </c>
       <c r="C64">
-        <v>520.5094688455035</v>
+        <v>514.6487142776087</v>
       </c>
       <c r="D64">
-        <v>891.4614688455036</v>
+        <v>894.0467142776088</v>
       </c>
       <c r="E64">
-        <v>44.85200000000003</v>
+        <v>53.29800000000006</v>
       </c>
       <c r="F64">
-        <v>523.652</v>
+        <v>532.0980000000001</v>
       </c>
       <c r="G64">
         <v>152.7</v>
@@ -6541,28 +6541,28 @@
         <v>144.775</v>
       </c>
       <c r="M64">
-        <v>28.9579556</v>
+        <v>29.4250194</v>
       </c>
       <c r="N64">
-        <v>115.8170444</v>
+        <v>115.3499806</v>
       </c>
       <c r="O64">
-        <v>26.05883498999999</v>
+        <v>25.953745635</v>
       </c>
       <c r="P64">
-        <v>89.75820940999998</v>
+        <v>89.39623496499999</v>
       </c>
       <c r="Q64">
-        <v>107.35820941</v>
+        <v>106.996234965</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3756256191184947</v>
+        <v>0.3836541020814745</v>
       </c>
       <c r="T64">
-        <v>2.299690182420266</v>
+        <v>2.355668318682203</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.999489673918831</v>
+        <v>4.920132694967737</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1689522427701456</v>
+        <v>0.1685951002752632</v>
       </c>
       <c r="C65">
-        <v>514.6487142776087</v>
+        <v>508.8029977853606</v>
       </c>
       <c r="D65">
-        <v>894.0467142776088</v>
+        <v>896.6469977853606</v>
       </c>
       <c r="E65">
-        <v>53.29800000000006</v>
+        <v>61.74399999999997</v>
       </c>
       <c r="F65">
-        <v>532.0980000000001</v>
+        <v>540.544</v>
       </c>
       <c r="G65">
         <v>152.7</v>
@@ -6623,28 +6623,28 @@
         <v>144.775</v>
       </c>
       <c r="M65">
-        <v>29.4250194</v>
+        <v>29.8920832</v>
       </c>
       <c r="N65">
-        <v>115.3499806</v>
+        <v>114.8829168</v>
       </c>
       <c r="O65">
-        <v>25.953745635</v>
+        <v>25.84865628</v>
       </c>
       <c r="P65">
-        <v>89.39623496499999</v>
+        <v>89.03426051999998</v>
       </c>
       <c r="Q65">
-        <v>106.996234965</v>
+        <v>106.63426052</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3836541020814745</v>
+        <v>0.3921286118757311</v>
       </c>
       <c r="T65">
-        <v>2.355668318682203</v>
+        <v>2.414756351403138</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.920132694967737</v>
+        <v>4.843255621608867</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1685951002752632</v>
+        <v>0.1682379577803808</v>
       </c>
       <c r="C66">
-        <v>508.8029977853606</v>
+        <v>502.9724509636333</v>
       </c>
       <c r="D66">
-        <v>896.6469977853606</v>
+        <v>899.2624509636332</v>
       </c>
       <c r="E66">
-        <v>61.74399999999997</v>
+        <v>70.19</v>
       </c>
       <c r="F66">
-        <v>540.544</v>
+        <v>548.99</v>
       </c>
       <c r="G66">
         <v>152.7</v>
@@ -6705,28 +6705,28 @@
         <v>144.775</v>
       </c>
       <c r="M66">
-        <v>29.8920832</v>
+        <v>30.359147</v>
       </c>
       <c r="N66">
-        <v>114.8829168</v>
+        <v>114.415853</v>
       </c>
       <c r="O66">
-        <v>25.84865628</v>
+        <v>25.74356692499999</v>
       </c>
       <c r="P66">
-        <v>89.03426051999998</v>
+        <v>88.67228607499997</v>
       </c>
       <c r="Q66">
-        <v>106.63426052</v>
+        <v>106.272286075</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3921286118757311</v>
+        <v>0.4010873793725165</v>
       </c>
       <c r="T66">
-        <v>2.414756351403138</v>
+        <v>2.477220843136697</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.843255621608867</v>
+        <v>4.768743996661039</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1682379577803808</v>
+        <v>0.1678808152854984</v>
       </c>
       <c r="C67">
-        <v>502.9724509636333</v>
+        <v>497.1572069472012</v>
       </c>
       <c r="D67">
-        <v>899.2624509636332</v>
+        <v>901.8932069472013</v>
       </c>
       <c r="E67">
-        <v>70.19</v>
+        <v>78.63600000000002</v>
       </c>
       <c r="F67">
-        <v>548.99</v>
+        <v>557.436</v>
       </c>
       <c r="G67">
         <v>152.7</v>
@@ -6787,28 +6787,28 @@
         <v>144.775</v>
       </c>
       <c r="M67">
-        <v>30.359147</v>
+        <v>30.8262108</v>
       </c>
       <c r="N67">
-        <v>114.415853</v>
+        <v>113.9487892</v>
       </c>
       <c r="O67">
-        <v>25.74356692499999</v>
+        <v>25.63847757</v>
       </c>
       <c r="P67">
-        <v>88.67228607499997</v>
+        <v>88.31031162999999</v>
       </c>
       <c r="Q67">
-        <v>106.272286075</v>
+        <v>105.91031163</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4010873793725165</v>
+        <v>0.4105731331926423</v>
       </c>
       <c r="T67">
-        <v>2.477220843136697</v>
+        <v>2.543359716736937</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.768743996661039</v>
+        <v>4.696490299741932</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1678808152854984</v>
+        <v>0.1675236727906159</v>
       </c>
       <c r="C68">
-        <v>497.1572069472012</v>
+        <v>491.3574004333336</v>
       </c>
       <c r="D68">
-        <v>901.8932069472013</v>
+        <v>904.5394004333338</v>
       </c>
       <c r="E68">
-        <v>78.63600000000002</v>
+        <v>87.08200000000005</v>
       </c>
       <c r="F68">
-        <v>557.436</v>
+        <v>565.8820000000001</v>
       </c>
       <c r="G68">
         <v>152.7</v>
@@ -6869,28 +6869,28 @@
         <v>144.775</v>
       </c>
       <c r="M68">
-        <v>30.8262108</v>
+        <v>31.2932746</v>
       </c>
       <c r="N68">
-        <v>113.9487892</v>
+        <v>113.4817254</v>
       </c>
       <c r="O68">
-        <v>25.63847757</v>
+        <v>25.533388215</v>
       </c>
       <c r="P68">
-        <v>88.31031162999999</v>
+        <v>87.94833718499999</v>
       </c>
       <c r="Q68">
-        <v>105.91031163</v>
+        <v>105.548337185</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4105731331926423</v>
+        <v>0.4206337811836848</v>
       </c>
       <c r="T68">
-        <v>2.543359716736937</v>
+        <v>2.613507006919008</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.696490299741932</v>
+        <v>4.626393429596529</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1675236727906159</v>
+        <v>0.1671665302957335</v>
       </c>
       <c r="C69">
-        <v>491.3574004333336</v>
+        <v>485.5731677047801</v>
       </c>
       <c r="D69">
-        <v>904.5394004333338</v>
+        <v>907.2011677047802</v>
       </c>
       <c r="E69">
-        <v>87.08200000000005</v>
+        <v>95.52800000000008</v>
       </c>
       <c r="F69">
-        <v>565.8820000000001</v>
+        <v>574.3280000000001</v>
       </c>
       <c r="G69">
         <v>152.7</v>
@@ -6951,28 +6951,28 @@
         <v>144.775</v>
       </c>
       <c r="M69">
-        <v>31.2932746</v>
+        <v>31.76033840000001</v>
       </c>
       <c r="N69">
-        <v>113.4817254</v>
+        <v>113.0146616</v>
       </c>
       <c r="O69">
-        <v>25.533388215</v>
+        <v>25.42829885999999</v>
       </c>
       <c r="P69">
-        <v>87.94833718499999</v>
+        <v>87.58636273999997</v>
       </c>
       <c r="Q69">
-        <v>105.548337185</v>
+        <v>105.18636274</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4206337811836848</v>
+        <v>0.4313232196741674</v>
       </c>
       <c r="T69">
-        <v>2.613507006919008</v>
+        <v>2.688038502737459</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.626393429596529</v>
+        <v>4.558358232102462</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1671665302957335</v>
+        <v>0.1681462628008511</v>
       </c>
       <c r="C70">
-        <v>485.5731677047801</v>
+        <v>469.8624221184946</v>
       </c>
       <c r="D70">
-        <v>907.2011677047802</v>
+        <v>899.9364221184948</v>
       </c>
       <c r="E70">
-        <v>95.52800000000008</v>
+        <v>103.9740000000001</v>
       </c>
       <c r="F70">
-        <v>574.3280000000001</v>
+        <v>582.7740000000001</v>
       </c>
       <c r="G70">
         <v>152.7</v>
@@ -7033,45 +7033,45 @@
         <v>144.775</v>
       </c>
       <c r="M70">
-        <v>31.76033840000001</v>
+        <v>33.68433720000001</v>
       </c>
       <c r="N70">
-        <v>113.0146616</v>
+        <v>111.0906628</v>
       </c>
       <c r="O70">
-        <v>25.42829885999999</v>
+        <v>24.99539912999999</v>
       </c>
       <c r="P70">
-        <v>87.58636273999997</v>
+        <v>86.09526366999997</v>
       </c>
       <c r="Q70">
-        <v>105.18636274</v>
+        <v>103.69526367</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4313232196741674</v>
+        <v>0.4427022993575844</v>
       </c>
       <c r="T70">
-        <v>2.688038502737459</v>
+        <v>2.767378482157101</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.225</v>
       </c>
       <c r="W70">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.558358232102462</v>
+        <v>4.297991649365152</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1681462628008511</v>
+        <v>0.1678084953059687</v>
       </c>
       <c r="C71">
-        <v>469.8624221184946</v>
+        <v>463.9078000351726</v>
       </c>
       <c r="D71">
-        <v>899.9364221184948</v>
+        <v>902.4278000351726</v>
       </c>
       <c r="E71">
-        <v>103.9740000000001</v>
+        <v>112.42</v>
       </c>
       <c r="F71">
-        <v>582.7740000000001</v>
+        <v>591.22</v>
       </c>
       <c r="G71">
         <v>152.7</v>
@@ -7115,28 +7115,28 @@
         <v>144.775</v>
       </c>
       <c r="M71">
-        <v>33.68433720000001</v>
+        <v>34.172516</v>
       </c>
       <c r="N71">
-        <v>111.0906628</v>
+        <v>110.602484</v>
       </c>
       <c r="O71">
-        <v>24.99539912999999</v>
+        <v>24.8855589</v>
       </c>
       <c r="P71">
-        <v>86.09526366999997</v>
+        <v>85.71692509999998</v>
       </c>
       <c r="Q71">
-        <v>103.69526367</v>
+        <v>103.3169251</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4427022993575844</v>
+        <v>0.4548399843532291</v>
       </c>
       <c r="T71">
-        <v>2.767378482157101</v>
+        <v>2.852007793538052</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.297991649365152</v>
+        <v>4.236591768659936</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1678084953059687</v>
+        <v>0.1674707278110863</v>
       </c>
       <c r="C72">
-        <v>463.9078000351726</v>
+        <v>457.9670104733267</v>
       </c>
       <c r="D72">
-        <v>902.4278000351726</v>
+        <v>904.9330104733267</v>
       </c>
       <c r="E72">
-        <v>112.42</v>
+        <v>120.866</v>
       </c>
       <c r="F72">
-        <v>591.22</v>
+        <v>599.6660000000001</v>
       </c>
       <c r="G72">
         <v>152.7</v>
@@ -7197,28 +7197,28 @@
         <v>144.775</v>
       </c>
       <c r="M72">
-        <v>34.172516</v>
+        <v>34.66069480000001</v>
       </c>
       <c r="N72">
-        <v>110.602484</v>
+        <v>110.1143052</v>
       </c>
       <c r="O72">
-        <v>24.8855589</v>
+        <v>24.77571866999999</v>
       </c>
       <c r="P72">
-        <v>85.71692509999998</v>
+        <v>85.33858652999997</v>
       </c>
       <c r="Q72">
-        <v>103.3169251</v>
+        <v>102.93858653</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4548399843532291</v>
+        <v>0.4678147510727115</v>
       </c>
       <c r="T72">
-        <v>2.852007793538052</v>
+        <v>2.942473609152172</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.236591768659936</v>
+        <v>4.176921462059092</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1674707278110863</v>
+        <v>0.1671329603162039</v>
       </c>
       <c r="C73">
-        <v>457.9670104733268</v>
+        <v>452.0401689541501</v>
       </c>
       <c r="D73">
-        <v>904.9330104733267</v>
+        <v>907.4521689541501</v>
       </c>
       <c r="E73">
-        <v>120.8659999999999</v>
+        <v>129.312</v>
       </c>
       <c r="F73">
-        <v>599.6659999999999</v>
+        <v>608.112</v>
       </c>
       <c r="G73">
         <v>152.7</v>
@@ -7279,28 +7279,28 @@
         <v>144.775</v>
       </c>
       <c r="M73">
-        <v>34.6606948</v>
+        <v>35.1488736</v>
       </c>
       <c r="N73">
-        <v>110.1143052</v>
+        <v>109.6261264</v>
       </c>
       <c r="O73">
-        <v>24.77571867</v>
+        <v>24.66587844</v>
       </c>
       <c r="P73">
-        <v>85.33858652999999</v>
+        <v>84.96024795999998</v>
       </c>
       <c r="Q73">
-        <v>102.93858653</v>
+        <v>102.56024796</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4678147510727114</v>
+        <v>0.4817162868435854</v>
       </c>
       <c r="T73">
-        <v>2.942473609152171</v>
+        <v>3.039401268738729</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.176921462059092</v>
+        <v>4.118908663974938</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1671329603162039</v>
+        <v>0.1667951928213215</v>
       </c>
       <c r="C74">
-        <v>452.0401689541501</v>
+        <v>446.1273922887819</v>
       </c>
       <c r="D74">
-        <v>907.4521689541501</v>
+        <v>909.9853922887819</v>
       </c>
       <c r="E74">
-        <v>129.312</v>
+        <v>137.758</v>
       </c>
       <c r="F74">
-        <v>608.112</v>
+        <v>616.558</v>
       </c>
       <c r="G74">
         <v>152.7</v>
@@ -7361,28 +7361,28 @@
         <v>144.775</v>
       </c>
       <c r="M74">
-        <v>35.1488736</v>
+        <v>35.6370524</v>
       </c>
       <c r="N74">
-        <v>109.6261264</v>
+        <v>109.1379476</v>
       </c>
       <c r="O74">
-        <v>24.66587844</v>
+        <v>24.55603820999999</v>
       </c>
       <c r="P74">
-        <v>84.96024795999998</v>
+        <v>84.58190938999998</v>
       </c>
       <c r="Q74">
-        <v>102.56024796</v>
+        <v>102.18190939</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4817162868435854</v>
+        <v>0.4966475660048943</v>
       </c>
       <c r="T74">
-        <v>3.039401268738729</v>
+        <v>3.143508754961327</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.118908663974938</v>
+        <v>4.062485257619117</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1667951928213215</v>
+        <v>0.1664574253264391</v>
       </c>
       <c r="C75">
-        <v>446.1273922887819</v>
+        <v>440.2287985963623</v>
       </c>
       <c r="D75">
-        <v>909.9853922887819</v>
+        <v>912.5327985963623</v>
       </c>
       <c r="E75">
-        <v>137.758</v>
+        <v>146.204</v>
       </c>
       <c r="F75">
-        <v>616.558</v>
+        <v>625.004</v>
       </c>
       <c r="G75">
         <v>152.7</v>
@@ -7443,28 +7443,28 @@
         <v>144.775</v>
       </c>
       <c r="M75">
-        <v>35.6370524</v>
+        <v>36.1252312</v>
       </c>
       <c r="N75">
-        <v>109.1379476</v>
+        <v>108.6497688</v>
       </c>
       <c r="O75">
-        <v>24.55603820999999</v>
+        <v>24.44619797999999</v>
       </c>
       <c r="P75">
-        <v>84.58190938999998</v>
+        <v>84.20357081999998</v>
       </c>
       <c r="Q75">
-        <v>102.18190939</v>
+        <v>101.80357082</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4966475660048943</v>
+        <v>0.5127274051016887</v>
       </c>
       <c r="T75">
-        <v>3.143508754961327</v>
+        <v>3.255624509354895</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.062485257619117</v>
+        <v>4.007586808191832</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1664574253264391</v>
+        <v>0.1681540328315567</v>
       </c>
       <c r="C76">
-        <v>440.2287985963623</v>
+        <v>419.1292721131285</v>
       </c>
       <c r="D76">
-        <v>912.5327985963623</v>
+        <v>899.8792721131285</v>
       </c>
       <c r="E76">
-        <v>146.204</v>
+        <v>154.65</v>
       </c>
       <c r="F76">
-        <v>625.004</v>
+        <v>633.45</v>
       </c>
       <c r="G76">
         <v>152.7</v>
@@ -7525,45 +7525,45 @@
         <v>144.775</v>
       </c>
       <c r="M76">
-        <v>36.1252312</v>
+        <v>38.830485</v>
       </c>
       <c r="N76">
-        <v>108.6497688</v>
+        <v>105.944515</v>
       </c>
       <c r="O76">
-        <v>24.44619797999999</v>
+        <v>23.83751587499999</v>
       </c>
       <c r="P76">
-        <v>84.20357081999998</v>
+        <v>82.10699912499997</v>
       </c>
       <c r="Q76">
-        <v>101.80357082</v>
+        <v>99.70699912499998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5127274051016887</v>
+        <v>0.5300936313262267</v>
       </c>
       <c r="T76">
-        <v>3.255624509354895</v>
+        <v>3.376709524099949</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.225</v>
       </c>
       <c r="W76">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.007586808191832</v>
+        <v>3.728385056225797</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1681540328315567</v>
+        <v>0.1678433903366743</v>
       </c>
       <c r="C77">
-        <v>419.1292721131285</v>
+        <v>412.9737750351713</v>
       </c>
       <c r="D77">
-        <v>899.8792721131285</v>
+        <v>902.1697750351714</v>
       </c>
       <c r="E77">
-        <v>154.65</v>
+        <v>163.0960000000001</v>
       </c>
       <c r="F77">
-        <v>633.45</v>
+        <v>641.8960000000001</v>
       </c>
       <c r="G77">
         <v>152.7</v>
@@ -7607,28 +7607,28 @@
         <v>144.775</v>
       </c>
       <c r="M77">
-        <v>38.830485</v>
+        <v>39.3482248</v>
       </c>
       <c r="N77">
-        <v>105.944515</v>
+        <v>105.4267752</v>
       </c>
       <c r="O77">
-        <v>23.83751587499999</v>
+        <v>23.72102442</v>
       </c>
       <c r="P77">
-        <v>82.10699912499997</v>
+        <v>81.70575077999999</v>
       </c>
       <c r="Q77">
-        <v>99.70699912499998</v>
+        <v>99.30575078</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5300936313262267</v>
+        <v>0.5489070430694761</v>
       </c>
       <c r="T77">
-        <v>3.376709524099949</v>
+        <v>3.507884956740423</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.728385056225797</v>
+        <v>3.679327358117563</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1678433903366743</v>
+        <v>0.1675327478417918</v>
       </c>
       <c r="C78">
-        <v>412.9737750351713</v>
+        <v>406.8299679511539</v>
       </c>
       <c r="D78">
-        <v>902.1697750351714</v>
+        <v>904.4719679511539</v>
       </c>
       <c r="E78">
-        <v>163.0960000000001</v>
+        <v>171.542</v>
       </c>
       <c r="F78">
-        <v>641.8960000000001</v>
+        <v>650.342</v>
       </c>
       <c r="G78">
         <v>152.7</v>
@@ -7689,28 +7689,28 @@
         <v>144.775</v>
       </c>
       <c r="M78">
-        <v>39.3482248</v>
+        <v>39.8659646</v>
       </c>
       <c r="N78">
-        <v>105.4267752</v>
+        <v>104.9090354</v>
       </c>
       <c r="O78">
-        <v>23.72102442</v>
+        <v>23.604532965</v>
       </c>
       <c r="P78">
-        <v>81.70575077999999</v>
+        <v>81.30450243499999</v>
       </c>
       <c r="Q78">
-        <v>99.30575078</v>
+        <v>98.904502435</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5489070430694761</v>
+        <v>0.5693564036599645</v>
       </c>
       <c r="T78">
-        <v>3.507884956740423</v>
+        <v>3.650466948740938</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.679327358117563</v>
+        <v>3.631543885934218</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1675327478417918</v>
+        <v>0.1672221053469094</v>
       </c>
       <c r="C79">
-        <v>406.8299679511539</v>
+        <v>400.6979405830136</v>
       </c>
       <c r="D79">
-        <v>904.4719679511539</v>
+        <v>906.7859405830137</v>
       </c>
       <c r="E79">
-        <v>171.542</v>
+        <v>179.988</v>
       </c>
       <c r="F79">
-        <v>650.342</v>
+        <v>658.788</v>
       </c>
       <c r="G79">
         <v>152.7</v>
@@ -7771,28 +7771,28 @@
         <v>144.775</v>
       </c>
       <c r="M79">
-        <v>39.8659646</v>
+        <v>40.3837044</v>
       </c>
       <c r="N79">
-        <v>104.9090354</v>
+        <v>104.3912956</v>
       </c>
       <c r="O79">
-        <v>23.604532965</v>
+        <v>23.48804151</v>
       </c>
       <c r="P79">
-        <v>81.30450243499999</v>
+        <v>80.90325408999999</v>
       </c>
       <c r="Q79">
-        <v>98.904502435</v>
+        <v>98.50325409</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5693564036599645</v>
+        <v>0.5916647970314065</v>
       </c>
       <c r="T79">
-        <v>3.650466948740938</v>
+        <v>3.806010940014228</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.631543885934218</v>
+        <v>3.584985630986344</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1672221053469094</v>
+        <v>0.166911462852027</v>
       </c>
       <c r="C80">
-        <v>400.6979405830136</v>
+        <v>394.5777835732116</v>
       </c>
       <c r="D80">
-        <v>906.7859405830137</v>
+        <v>909.1117835732116</v>
       </c>
       <c r="E80">
-        <v>179.988</v>
+        <v>188.434</v>
       </c>
       <c r="F80">
-        <v>658.788</v>
+        <v>667.234</v>
       </c>
       <c r="G80">
         <v>152.7</v>
@@ -7853,28 +7853,28 @@
         <v>144.775</v>
       </c>
       <c r="M80">
-        <v>40.3837044</v>
+        <v>40.9014442</v>
       </c>
       <c r="N80">
-        <v>104.3912956</v>
+        <v>103.8735558</v>
       </c>
       <c r="O80">
-        <v>23.48804151</v>
+        <v>23.371550055</v>
       </c>
       <c r="P80">
-        <v>80.90325408999999</v>
+        <v>80.50200574499998</v>
       </c>
       <c r="Q80">
-        <v>98.50325409</v>
+        <v>98.10200574499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5916647970314065</v>
+        <v>0.6160977992953669</v>
       </c>
       <c r="T80">
-        <v>3.806010940014228</v>
+        <v>3.976368644742117</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.584985630986344</v>
+        <v>3.539606066037149</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.166911462852027</v>
+        <v>0.1683368203571446</v>
       </c>
       <c r="C81">
-        <v>394.5777835732116</v>
+        <v>375.5569269714963</v>
       </c>
       <c r="D81">
-        <v>909.1117835732116</v>
+        <v>898.5369269714963</v>
       </c>
       <c r="E81">
-        <v>188.434</v>
+        <v>196.8800000000001</v>
       </c>
       <c r="F81">
-        <v>667.234</v>
+        <v>675.6800000000001</v>
       </c>
       <c r="G81">
         <v>152.7</v>
@@ -7935,45 +7935,45 @@
         <v>144.775</v>
       </c>
       <c r="M81">
-        <v>40.9014442</v>
+        <v>43.31108800000001</v>
       </c>
       <c r="N81">
-        <v>103.8735558</v>
+        <v>101.463912</v>
       </c>
       <c r="O81">
-        <v>23.371550055</v>
+        <v>22.82938019999999</v>
       </c>
       <c r="P81">
-        <v>80.50200574499998</v>
+        <v>78.63453179999998</v>
       </c>
       <c r="Q81">
-        <v>98.10200574499999</v>
+        <v>96.23453179999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6160977992953669</v>
+        <v>0.6429741017857233</v>
       </c>
       <c r="T81">
-        <v>3.976368644742117</v>
+        <v>4.163762119942795</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0.225</v>
       </c>
       <c r="W81">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.539606066037149</v>
+        <v>3.342677514820222</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1683368203571446</v>
+        <v>0.1680478778622622</v>
       </c>
       <c r="C82">
-        <v>375.5569269714963</v>
+        <v>369.2346898209067</v>
       </c>
       <c r="D82">
-        <v>898.5369269714963</v>
+        <v>900.6606898209068</v>
       </c>
       <c r="E82">
-        <v>196.8800000000001</v>
+        <v>205.3260000000001</v>
       </c>
       <c r="F82">
-        <v>675.6800000000001</v>
+        <v>684.1260000000001</v>
       </c>
       <c r="G82">
         <v>152.7</v>
@@ -8017,28 +8017,28 @@
         <v>144.775</v>
       </c>
       <c r="M82">
-        <v>43.31108800000001</v>
+        <v>43.85247660000001</v>
       </c>
       <c r="N82">
-        <v>101.463912</v>
+        <v>100.9225234</v>
       </c>
       <c r="O82">
-        <v>22.82938019999999</v>
+        <v>22.70756776499999</v>
       </c>
       <c r="P82">
-        <v>78.63453179999998</v>
+        <v>78.21495563499997</v>
       </c>
       <c r="Q82">
-        <v>96.23453179999998</v>
+        <v>95.81495563499998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6429741017857233</v>
+        <v>0.6726794887487486</v>
       </c>
       <c r="T82">
-        <v>4.163762119942795</v>
+        <v>4.370881224111964</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.342677514820222</v>
+        <v>3.301409891180466</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1680478778622622</v>
+        <v>0.1677589353673798</v>
       </c>
       <c r="C83">
-        <v>369.2346898209067</v>
+        <v>362.9225158171359</v>
       </c>
       <c r="D83">
-        <v>900.6606898209068</v>
+        <v>902.7945158171361</v>
       </c>
       <c r="E83">
-        <v>205.3260000000001</v>
+        <v>213.7720000000001</v>
       </c>
       <c r="F83">
-        <v>684.1260000000001</v>
+        <v>692.5720000000001</v>
       </c>
       <c r="G83">
         <v>152.7</v>
@@ -8099,28 +8099,28 @@
         <v>144.775</v>
       </c>
       <c r="M83">
-        <v>43.85247660000001</v>
+        <v>44.39386520000001</v>
       </c>
       <c r="N83">
-        <v>100.9225234</v>
+        <v>100.3811348</v>
       </c>
       <c r="O83">
-        <v>22.70756776499999</v>
+        <v>22.58575532999999</v>
       </c>
       <c r="P83">
-        <v>78.21495563499997</v>
+        <v>77.79537946999997</v>
       </c>
       <c r="Q83">
-        <v>95.81495563499998</v>
+        <v>95.39537946999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6726794887487486</v>
+        <v>0.7056854742632213</v>
       </c>
       <c r="T83">
-        <v>4.370881224111964</v>
+        <v>4.601013562077709</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.301409891180466</v>
+        <v>3.261148794946558</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1677589353673798</v>
+        <v>0.1674699928724974</v>
       </c>
       <c r="C84">
-        <v>362.9225158171359</v>
+        <v>356.6204766542153</v>
       </c>
       <c r="D84">
-        <v>902.7945158171361</v>
+        <v>904.9384766542154</v>
       </c>
       <c r="E84">
-        <v>213.7720000000001</v>
+        <v>222.218</v>
       </c>
       <c r="F84">
-        <v>692.5720000000001</v>
+        <v>701.018</v>
       </c>
       <c r="G84">
         <v>152.7</v>
@@ -8181,28 +8181,28 @@
         <v>144.775</v>
       </c>
       <c r="M84">
-        <v>44.39386520000001</v>
+        <v>44.93525380000001</v>
       </c>
       <c r="N84">
-        <v>100.3811348</v>
+        <v>99.83974619999998</v>
       </c>
       <c r="O84">
-        <v>22.58575532999999</v>
+        <v>22.463942895</v>
       </c>
       <c r="P84">
-        <v>77.79537946999997</v>
+        <v>77.37580330499998</v>
       </c>
       <c r="Q84">
-        <v>95.39537946999998</v>
+        <v>94.97580330499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7056854742632213</v>
+        <v>0.7425745168970437</v>
       </c>
       <c r="T84">
-        <v>4.601013562077709</v>
+        <v>4.858220292745306</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.261148794946558</v>
+        <v>3.221857845609853</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1674699928724974</v>
+        <v>0.167181050377615</v>
       </c>
       <c r="C85">
-        <v>356.6204766542153</v>
+        <v>350.3286447088343</v>
       </c>
       <c r="D85">
-        <v>904.9384766542154</v>
+        <v>907.0926447088344</v>
       </c>
       <c r="E85">
-        <v>222.218</v>
+        <v>230.664</v>
       </c>
       <c r="F85">
-        <v>701.018</v>
+        <v>709.4640000000001</v>
       </c>
       <c r="G85">
         <v>152.7</v>
@@ -8263,28 +8263,28 @@
         <v>144.775</v>
       </c>
       <c r="M85">
-        <v>44.93525380000001</v>
+        <v>45.47664240000001</v>
       </c>
       <c r="N85">
-        <v>99.83974619999998</v>
+        <v>99.29835759999997</v>
       </c>
       <c r="O85">
-        <v>22.463942895</v>
+        <v>22.34213046</v>
       </c>
       <c r="P85">
-        <v>77.37580330499998</v>
+        <v>76.95622713999998</v>
       </c>
       <c r="Q85">
-        <v>94.97580330499999</v>
+        <v>94.55622713999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7425745168970437</v>
+        <v>0.784074689860094</v>
       </c>
       <c r="T85">
-        <v>4.858220292745306</v>
+        <v>5.147577864746353</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.221857845609853</v>
+        <v>3.183502395066879</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.167181050377615</v>
+        <v>0.1668921078827326</v>
       </c>
       <c r="C86">
-        <v>350.3286447088344</v>
+        <v>344.0470930484856</v>
       </c>
       <c r="D86">
-        <v>907.0926447088344</v>
+        <v>909.2570930484857</v>
       </c>
       <c r="E86">
-        <v>230.6639999999999</v>
+        <v>239.11</v>
       </c>
       <c r="F86">
-        <v>709.4639999999999</v>
+        <v>717.91</v>
       </c>
       <c r="G86">
         <v>152.7</v>
@@ -8345,28 +8345,28 @@
         <v>144.775</v>
       </c>
       <c r="M86">
-        <v>45.4766424</v>
+        <v>46.018031</v>
       </c>
       <c r="N86">
-        <v>99.29835759999997</v>
+        <v>98.75696899999997</v>
       </c>
       <c r="O86">
-        <v>22.34213046</v>
+        <v>22.22031802499999</v>
       </c>
       <c r="P86">
-        <v>76.95622713999998</v>
+        <v>76.53665097499997</v>
       </c>
       <c r="Q86">
-        <v>94.55622713999999</v>
+        <v>94.13665097499998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7840746898600935</v>
+        <v>0.8311082192182172</v>
       </c>
       <c r="T86">
-        <v>5.147577864746349</v>
+        <v>5.475516446347536</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.183502395066879</v>
+        <v>3.146049425713151</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1668921078827326</v>
+        <v>0.1666031653878502</v>
       </c>
       <c r="C87">
-        <v>344.0470930484856</v>
+        <v>337.7758954397264</v>
       </c>
       <c r="D87">
-        <v>909.2570930484857</v>
+        <v>911.4318954397263</v>
       </c>
       <c r="E87">
-        <v>239.11</v>
+        <v>247.556</v>
       </c>
       <c r="F87">
-        <v>717.91</v>
+        <v>726.356</v>
       </c>
       <c r="G87">
         <v>152.7</v>
@@ -8427,28 +8427,28 @@
         <v>144.775</v>
       </c>
       <c r="M87">
-        <v>46.018031</v>
+        <v>46.55941960000001</v>
       </c>
       <c r="N87">
-        <v>98.75696899999997</v>
+        <v>98.21558039999996</v>
       </c>
       <c r="O87">
-        <v>22.22031802499999</v>
+        <v>22.09850558999999</v>
       </c>
       <c r="P87">
-        <v>76.53665097499997</v>
+        <v>76.11707480999998</v>
       </c>
       <c r="Q87">
-        <v>94.13665097499998</v>
+        <v>93.71707480999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8311082192182172</v>
+        <v>0.8848608241989298</v>
       </c>
       <c r="T87">
-        <v>5.475516446347536</v>
+        <v>5.85030339674889</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.146049425713151</v>
+        <v>3.109467455646719</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1666031653878502</v>
+        <v>0.1663142228929678</v>
       </c>
       <c r="C88">
-        <v>337.7758954397264</v>
+        <v>331.5151263565589</v>
       </c>
       <c r="D88">
-        <v>911.4318954397263</v>
+        <v>913.617126356559</v>
       </c>
       <c r="E88">
-        <v>247.556</v>
+        <v>256.002</v>
       </c>
       <c r="F88">
-        <v>726.356</v>
+        <v>734.802</v>
       </c>
       <c r="G88">
         <v>152.7</v>
@@ -8509,28 +8509,28 @@
         <v>144.775</v>
       </c>
       <c r="M88">
-        <v>46.55941960000001</v>
+        <v>47.1008082</v>
       </c>
       <c r="N88">
-        <v>98.21558039999996</v>
+        <v>97.67419179999997</v>
       </c>
       <c r="O88">
-        <v>22.09850558999999</v>
+        <v>21.976693155</v>
       </c>
       <c r="P88">
-        <v>76.11707480999998</v>
+        <v>75.69749864499998</v>
       </c>
       <c r="Q88">
-        <v>93.71707480999999</v>
+        <v>93.29749864499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8848608241989298</v>
+        <v>0.9468830607151366</v>
       </c>
       <c r="T88">
-        <v>5.85030339674889</v>
+        <v>6.282749877981223</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.109467455646719</v>
+        <v>3.0737264504094</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1663142228929678</v>
+        <v>0.1660252803980854</v>
       </c>
       <c r="C89">
-        <v>331.5151263565589</v>
+        <v>325.2648609889313</v>
       </c>
       <c r="D89">
-        <v>913.617126356559</v>
+        <v>915.8128609889313</v>
       </c>
       <c r="E89">
-        <v>256.002</v>
+        <v>264.448</v>
       </c>
       <c r="F89">
-        <v>734.802</v>
+        <v>743.248</v>
       </c>
       <c r="G89">
         <v>152.7</v>
@@ -8591,28 +8591,28 @@
         <v>144.775</v>
       </c>
       <c r="M89">
-        <v>47.1008082</v>
+        <v>47.64219680000001</v>
       </c>
       <c r="N89">
-        <v>97.67419179999997</v>
+        <v>97.13280319999997</v>
       </c>
       <c r="O89">
-        <v>21.976693155</v>
+        <v>21.85488071999999</v>
       </c>
       <c r="P89">
-        <v>75.69749864499998</v>
+        <v>75.27792247999997</v>
       </c>
       <c r="Q89">
-        <v>93.29749864499999</v>
+        <v>92.87792247999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9468830607151366</v>
+        <v>1.019242336650711</v>
       </c>
       <c r="T89">
-        <v>6.282749877981223</v>
+        <v>6.787270772752278</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.0737264504094</v>
+        <v>3.038797740745657</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1660252803980854</v>
+        <v>0.165736337903203</v>
       </c>
       <c r="C90">
-        <v>325.2648609889313</v>
+        <v>319.0251752513619</v>
       </c>
       <c r="D90">
-        <v>915.8128609889313</v>
+        <v>918.019175251362</v>
       </c>
       <c r="E90">
-        <v>264.448</v>
+        <v>272.8940000000001</v>
       </c>
       <c r="F90">
-        <v>743.248</v>
+        <v>751.6940000000001</v>
       </c>
       <c r="G90">
         <v>152.7</v>
@@ -8673,28 +8673,28 @@
         <v>144.775</v>
       </c>
       <c r="M90">
-        <v>47.64219680000001</v>
+        <v>48.18358540000001</v>
       </c>
       <c r="N90">
-        <v>97.13280319999997</v>
+        <v>96.59141459999998</v>
       </c>
       <c r="O90">
-        <v>21.85488071999999</v>
+        <v>21.73306828499999</v>
       </c>
       <c r="P90">
-        <v>75.27792247999997</v>
+        <v>74.85834631499998</v>
       </c>
       <c r="Q90">
-        <v>92.87792247999998</v>
+        <v>92.45834631499999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.019242336650711</v>
+        <v>1.104757844574572</v>
       </c>
       <c r="T90">
-        <v>6.787270772752278</v>
+        <v>7.383522739299888</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.038797740745657</v>
+        <v>3.004653945905818</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.165736337903203</v>
+        <v>0.1708878954083206</v>
       </c>
       <c r="C91">
-        <v>319.0251752513619</v>
+        <v>272.7719313396266</v>
       </c>
       <c r="D91">
-        <v>918.019175251362</v>
+        <v>880.2119313396265</v>
       </c>
       <c r="E91">
-        <v>272.8940000000001</v>
+        <v>281.34</v>
       </c>
       <c r="F91">
-        <v>751.6940000000001</v>
+        <v>760.14</v>
       </c>
       <c r="G91">
         <v>152.7</v>
@@ -8755,45 +8755,45 @@
         <v>144.775</v>
       </c>
       <c r="M91">
-        <v>48.18358540000001</v>
+        <v>54.654066</v>
       </c>
       <c r="N91">
-        <v>96.59141459999998</v>
+        <v>90.12093399999998</v>
       </c>
       <c r="O91">
-        <v>21.73306828499999</v>
+        <v>20.27721014999999</v>
       </c>
       <c r="P91">
-        <v>74.85834631499998</v>
+        <v>69.84372384999998</v>
       </c>
       <c r="Q91">
-        <v>92.45834631499999</v>
+        <v>87.44372384999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.104757844574572</v>
+        <v>1.207376454083206</v>
       </c>
       <c r="T91">
-        <v>7.383522739299888</v>
+        <v>8.099025099157021</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.225</v>
       </c>
       <c r="W91">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.004653945905818</v>
+        <v>2.648933749961073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1708878954083206</v>
+        <v>0.1706594029134381</v>
       </c>
       <c r="C92">
-        <v>272.7719313396266</v>
+        <v>265.9367176762912</v>
       </c>
       <c r="D92">
-        <v>880.2119313396265</v>
+        <v>881.8227176762913</v>
       </c>
       <c r="E92">
-        <v>281.34</v>
+        <v>289.786</v>
       </c>
       <c r="F92">
-        <v>760.14</v>
+        <v>768.586</v>
       </c>
       <c r="G92">
         <v>152.7</v>
@@ -8837,28 +8837,28 @@
         <v>144.775</v>
       </c>
       <c r="M92">
-        <v>54.654066</v>
+        <v>55.26133340000001</v>
       </c>
       <c r="N92">
-        <v>90.12093399999998</v>
+        <v>89.51366659999997</v>
       </c>
       <c r="O92">
-        <v>20.27721014999999</v>
+        <v>20.14057498499999</v>
       </c>
       <c r="P92">
-        <v>69.84372384999998</v>
+        <v>69.37309161499996</v>
       </c>
       <c r="Q92">
-        <v>87.44372384999998</v>
+        <v>86.97309161499997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.207376454083206</v>
+        <v>1.332799199038202</v>
       </c>
       <c r="T92">
-        <v>8.099025099157021</v>
+        <v>8.97352798342685</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.648933749961073</v>
+        <v>2.619824587873588</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1706594029134381</v>
+        <v>0.1704309104185557</v>
       </c>
       <c r="C93">
-        <v>265.9367176762912</v>
+        <v>259.1074102939505</v>
       </c>
       <c r="D93">
-        <v>881.8227176762913</v>
+        <v>883.4394102939505</v>
       </c>
       <c r="E93">
-        <v>289.786</v>
+        <v>298.232</v>
       </c>
       <c r="F93">
-        <v>768.586</v>
+        <v>777.032</v>
       </c>
       <c r="G93">
         <v>152.7</v>
@@ -8919,28 +8919,28 @@
         <v>144.775</v>
       </c>
       <c r="M93">
-        <v>55.26133340000001</v>
+        <v>55.86860080000001</v>
       </c>
       <c r="N93">
-        <v>89.51366659999997</v>
+        <v>88.90639919999997</v>
       </c>
       <c r="O93">
-        <v>20.14057498499999</v>
+        <v>20.00393981999999</v>
       </c>
       <c r="P93">
-        <v>69.37309161499996</v>
+        <v>68.90245937999998</v>
       </c>
       <c r="Q93">
-        <v>86.97309161499997</v>
+        <v>86.50245937999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.332799199038202</v>
+        <v>1.489577630231947</v>
       </c>
       <c r="T93">
-        <v>8.97352798342685</v>
+        <v>10.06665658876414</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.619824587873588</v>
+        <v>2.591348233657571</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1704309104185557</v>
+        <v>0.1702024179236733</v>
       </c>
       <c r="C94">
-        <v>259.1074102939505</v>
+        <v>252.2840417371701</v>
       </c>
       <c r="D94">
-        <v>883.4394102939505</v>
+        <v>885.0620417371703</v>
       </c>
       <c r="E94">
-        <v>298.232</v>
+        <v>306.6780000000001</v>
       </c>
       <c r="F94">
-        <v>777.032</v>
+        <v>785.4780000000001</v>
       </c>
       <c r="G94">
         <v>152.7</v>
@@ -9001,28 +9001,28 @@
         <v>144.775</v>
       </c>
       <c r="M94">
-        <v>55.86860080000001</v>
+        <v>56.47586820000001</v>
       </c>
       <c r="N94">
-        <v>88.90639919999997</v>
+        <v>88.29913179999997</v>
       </c>
       <c r="O94">
-        <v>20.00393981999999</v>
+        <v>19.86730465499999</v>
       </c>
       <c r="P94">
-        <v>68.90245937999998</v>
+        <v>68.43182714499997</v>
       </c>
       <c r="Q94">
-        <v>86.50245937999999</v>
+        <v>86.03182714499998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.489577630231947</v>
+        <v>1.69114989890962</v>
       </c>
       <c r="T94">
-        <v>10.06665658876414</v>
+        <v>11.47210765276922</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.591348233657571</v>
+        <v>2.563484274155877</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1702024179236733</v>
+        <v>0.1699739254287909</v>
       </c>
       <c r="C95">
-        <v>252.2840417371701</v>
+        <v>245.4666447900566</v>
       </c>
       <c r="D95">
-        <v>885.0620417371703</v>
+        <v>886.6906447900568</v>
       </c>
       <c r="E95">
-        <v>306.6780000000001</v>
+        <v>315.1240000000001</v>
       </c>
       <c r="F95">
-        <v>785.4780000000001</v>
+        <v>793.9240000000001</v>
       </c>
       <c r="G95">
         <v>152.7</v>
@@ -9083,28 +9083,28 @@
         <v>144.775</v>
       </c>
       <c r="M95">
-        <v>56.47586820000001</v>
+        <v>57.08313560000001</v>
       </c>
       <c r="N95">
-        <v>88.29913179999997</v>
+        <v>87.69186439999996</v>
       </c>
       <c r="O95">
-        <v>19.86730465499999</v>
+        <v>19.73066948999999</v>
       </c>
       <c r="P95">
-        <v>68.43182714499997</v>
+        <v>67.96119490999996</v>
       </c>
       <c r="Q95">
-        <v>86.03182714499998</v>
+        <v>85.56119490999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.69114989890962</v>
+        <v>1.959912923813183</v>
       </c>
       <c r="T95">
-        <v>11.47210765276922</v>
+        <v>13.346042404776</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.563484274155877</v>
+        <v>2.536213164856346</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1699739254287909</v>
+        <v>0.1697454329339085</v>
       </c>
       <c r="C96">
-        <v>245.4666447900566</v>
+        <v>238.6552524784661</v>
       </c>
       <c r="D96">
-        <v>886.6906447900568</v>
+        <v>888.3252524784662</v>
       </c>
       <c r="E96">
-        <v>315.1240000000001</v>
+        <v>323.5700000000001</v>
       </c>
       <c r="F96">
-        <v>793.9240000000001</v>
+        <v>802.3700000000001</v>
       </c>
       <c r="G96">
         <v>152.7</v>
@@ -9165,28 +9165,28 @@
         <v>144.775</v>
       </c>
       <c r="M96">
-        <v>57.08313560000001</v>
+        <v>57.69040300000001</v>
       </c>
       <c r="N96">
-        <v>87.69186439999996</v>
+        <v>87.08459699999997</v>
       </c>
       <c r="O96">
-        <v>19.73066948999999</v>
+        <v>19.594034325</v>
       </c>
       <c r="P96">
-        <v>67.96119490999996</v>
+        <v>67.49056267499998</v>
       </c>
       <c r="Q96">
-        <v>85.56119490999997</v>
+        <v>85.09056267499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.959912923813183</v>
+        <v>2.336181158678173</v>
       </c>
       <c r="T96">
-        <v>13.346042404776</v>
+        <v>15.96955105758549</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.536213164856346</v>
+        <v>2.509516184173648</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1697454329339085</v>
+        <v>0.1724185404390261</v>
       </c>
       <c r="C97">
-        <v>238.6552524784661</v>
+        <v>211.4553725873202</v>
       </c>
       <c r="D97">
-        <v>888.3252524784662</v>
+        <v>869.5713725873203</v>
       </c>
       <c r="E97">
-        <v>323.5700000000001</v>
+        <v>332.016</v>
       </c>
       <c r="F97">
-        <v>802.3700000000001</v>
+        <v>810.816</v>
       </c>
       <c r="G97">
         <v>152.7</v>
@@ -9247,45 +9247,45 @@
         <v>144.775</v>
       </c>
       <c r="M97">
-        <v>57.69040300000001</v>
+        <v>61.45985280000001</v>
       </c>
       <c r="N97">
-        <v>87.08459699999997</v>
+        <v>83.31514719999997</v>
       </c>
       <c r="O97">
-        <v>19.594034325</v>
+        <v>18.74590811999999</v>
       </c>
       <c r="P97">
-        <v>67.49056267499998</v>
+        <v>64.56923907999997</v>
       </c>
       <c r="Q97">
-        <v>85.09056267499999</v>
+        <v>82.16923907999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.336181158678173</v>
+        <v>2.900583510975657</v>
       </c>
       <c r="T97">
-        <v>15.96955105758549</v>
+        <v>19.90481403679973</v>
       </c>
       <c r="U97">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V97">
         <v>0.225</v>
       </c>
       <c r="W97">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.509516184173648</v>
+        <v>2.355602778143978</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1724185404390261</v>
+        <v>0.1722202729441437</v>
       </c>
       <c r="C98">
-        <v>211.4553725873204</v>
+        <v>204.3731391229337</v>
       </c>
       <c r="D98">
-        <v>869.5713725873205</v>
+        <v>870.9351391229337</v>
       </c>
       <c r="E98">
-        <v>332.016</v>
+        <v>340.4619999999999</v>
       </c>
       <c r="F98">
-        <v>810.816</v>
+        <v>819.2619999999999</v>
       </c>
       <c r="G98">
         <v>152.7</v>
@@ -9329,28 +9329,28 @@
         <v>144.775</v>
       </c>
       <c r="M98">
-        <v>61.45985280000001</v>
+        <v>62.1000596</v>
       </c>
       <c r="N98">
-        <v>83.31514719999997</v>
+        <v>82.67494039999997</v>
       </c>
       <c r="O98">
-        <v>18.74590811999999</v>
+        <v>18.60186159</v>
       </c>
       <c r="P98">
-        <v>64.56923907999997</v>
+        <v>64.07307880999997</v>
       </c>
       <c r="Q98">
-        <v>82.16923907999998</v>
+        <v>81.67307880999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.900583510975649</v>
+        <v>3.841254098138119</v>
       </c>
       <c r="T98">
-        <v>19.90481403679968</v>
+        <v>26.46358566882338</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.355602778143978</v>
+        <v>2.331318213420845</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1722202729441437</v>
+        <v>0.1720220054492613</v>
       </c>
       <c r="C99">
-        <v>204.3731391229337</v>
+        <v>197.2951900236018</v>
       </c>
       <c r="D99">
-        <v>870.9351391229337</v>
+        <v>872.3031900236017</v>
       </c>
       <c r="E99">
-        <v>340.4619999999999</v>
+        <v>348.908</v>
       </c>
       <c r="F99">
-        <v>819.2619999999999</v>
+        <v>827.708</v>
       </c>
       <c r="G99">
         <v>152.7</v>
@@ -9411,28 +9411,28 @@
         <v>144.775</v>
       </c>
       <c r="M99">
-        <v>62.1000596</v>
+        <v>62.7402664</v>
       </c>
       <c r="N99">
-        <v>82.67494039999997</v>
+        <v>82.03473359999998</v>
       </c>
       <c r="O99">
-        <v>18.60186159</v>
+        <v>18.45781506</v>
       </c>
       <c r="P99">
-        <v>64.07307880999997</v>
+        <v>63.57691853999998</v>
       </c>
       <c r="Q99">
-        <v>81.67307880999998</v>
+        <v>81.17691853999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.841254098138119</v>
+        <v>5.722595272463058</v>
       </c>
       <c r="T99">
-        <v>26.46358566882338</v>
+        <v>39.58112893287079</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.331318213420845</v>
+        <v>2.307529252059408</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1720220054492613</v>
+        <v>0.1718237379543789</v>
       </c>
       <c r="C100">
-        <v>197.2951900236018</v>
+        <v>190.221545510522</v>
       </c>
       <c r="D100">
-        <v>872.3031900236017</v>
+        <v>873.6755455105221</v>
       </c>
       <c r="E100">
-        <v>348.908</v>
+        <v>357.354</v>
       </c>
       <c r="F100">
-        <v>827.708</v>
+        <v>836.154</v>
       </c>
       <c r="G100">
         <v>152.7</v>
@@ -9493,28 +9493,28 @@
         <v>144.775</v>
       </c>
       <c r="M100">
-        <v>62.7402664</v>
+        <v>63.3804732</v>
       </c>
       <c r="N100">
-        <v>82.03473359999998</v>
+        <v>81.39452679999997</v>
       </c>
       <c r="O100">
-        <v>18.45781506</v>
+        <v>18.31376852999999</v>
       </c>
       <c r="P100">
-        <v>63.57691853999998</v>
+        <v>63.08075826999998</v>
       </c>
       <c r="Q100">
-        <v>81.17691853999999</v>
+        <v>80.68075826999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.722595272463058</v>
+        <v>11.36661879543788</v>
       </c>
       <c r="T100">
-        <v>39.58112893287079</v>
+        <v>78.93375872501302</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.307529252059408</v>
+        <v>2.284220875775979</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1718237379543789</v>
-      </c>
-      <c r="C101">
-        <v>190.221545510522</v>
-      </c>
-      <c r="D101">
-        <v>873.6755455105221</v>
-      </c>
-      <c r="E101">
-        <v>357.354</v>
-      </c>
-      <c r="F101">
-        <v>836.154</v>
-      </c>
-      <c r="G101">
-        <v>152.7</v>
-      </c>
-      <c r="H101">
-        <v>365.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>162.375</v>
-      </c>
-      <c r="K101">
-        <v>17.60000000000001</v>
-      </c>
-      <c r="L101">
-        <v>144.775</v>
-      </c>
-      <c r="M101">
-        <v>63.3804732</v>
-      </c>
-      <c r="N101">
-        <v>81.39452679999997</v>
-      </c>
-      <c r="O101">
-        <v>18.31376852999999</v>
-      </c>
-      <c r="P101">
-        <v>63.08075826999998</v>
-      </c>
-      <c r="Q101">
-        <v>80.68075826999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.36661879543788</v>
-      </c>
-      <c r="T101">
-        <v>78.93375872501302</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.225</v>
-      </c>
-      <c r="W101">
-        <v>0.05874500000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.284220875775979</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
